--- a/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>HAE</t>
   </si>
@@ -656,411 +656,423 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44191</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>336300</v>
+      </c>
+      <c r="E8" s="3">
         <v>318200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>311300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>304400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>305300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>297500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>261500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>265000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>259800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>239900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>228500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>225000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>240400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>209500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>195600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>238500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>259000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>252600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>238500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>249300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>247400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>241600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>229300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>233600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>234000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>225400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>211000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>228100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>227800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>151300</v>
+      </c>
+      <c r="E9" s="3">
         <v>147600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>143900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>148200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>146600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>139600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>119400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>128700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>121400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>117100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>118200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>143100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>120200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>104000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>105000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>124900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>130900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>125600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>122500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>138100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>136200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>129700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>124900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>129200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>122700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>120800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>119300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>146000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>126800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E10" s="3">
         <v>170600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>167400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>156200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>158700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>157900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>142100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>136300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>138400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>122800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>110300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>82000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>120200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>105500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>90600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>113600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>128100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>127000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>116000</v>
-      </c>
-      <c r="V10" s="3">
-        <v>111200</v>
       </c>
       <c r="W10" s="3">
         <v>111200</v>
       </c>
       <c r="X10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="Y10" s="3">
         <v>111900</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>104400</v>
       </c>
       <c r="Z10" s="3">
         <v>104400</v>
       </c>
       <c r="AA10" s="3">
+        <v>104400</v>
+      </c>
+      <c r="AB10" s="3">
         <v>111300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>104600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>91700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>82100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>101000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1093,100 +1105,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E12" s="3">
         <v>12700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>10900</v>
       </c>
       <c r="I12" s="3">
         <v>10900</v>
       </c>
       <c r="J12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K12" s="3">
         <v>13200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>11100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>12400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>8200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>8500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1277,138 +1293,144 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E14" s="3">
         <v>12800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>16600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>51700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>24500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>31700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>57200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>400</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E15" s="3">
         <v>7200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>32800</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>10</v>
@@ -1422,8 +1444,8 @@
       <c r="S15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1461,8 +1483,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1492,192 +1517,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>290300</v>
+      </c>
+      <c r="E17" s="3">
         <v>282900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>257700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>269200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>262000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>250800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>230700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>245800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>224100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>215400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>227100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>246200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>199900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>150700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>183900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>212500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>218100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>202800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>251800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>225400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>219000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>215500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>224100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>219300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>233000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>201100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>186300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>285600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>206600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E18" s="3">
         <v>35300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>53600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>35200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>43300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>46700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>35700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>58800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>40900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>49800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-13300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>23900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>28400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>26100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-57500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>21200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1710,192 +1742,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-3800</v>
       </c>
       <c r="Q20" s="3">
         <v>-3800</v>
       </c>
       <c r="R20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="S20" s="3">
         <v>-4100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-1400</v>
       </c>
       <c r="AC20" s="3">
         <v>-1400</v>
       </c>
       <c r="AD20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E21" s="3">
         <v>55800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>74600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>56500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>65800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>64500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>47900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>40100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>55800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>43500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>25000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>58100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>75800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>28700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>50700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>64900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>72100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>51600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>53400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>48300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>29700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>36300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>22500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>45100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>45000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>41200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1926,11 +1965,11 @@
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3">
         <v>3000</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>10</v>
@@ -1947,8 +1986,8 @@
       <c r="S22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1986,192 +2025,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E23" s="3">
         <v>32800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>51600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>32600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>42200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>41100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>19900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-27400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>37400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>55000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>37800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>45100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-17700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>21800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>25500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>23000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>13300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>22900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>23300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-59200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>18900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E24" s="3">
         <v>7900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7900</v>
-      </c>
-      <c r="I24" s="3">
-        <v>5600</v>
       </c>
       <c r="J24" s="3">
         <v>5600</v>
       </c>
       <c r="K24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="L24" s="3">
         <v>8200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-16400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-9200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-21300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2262,192 +2310,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E26" s="3">
         <v>24900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>41000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>32900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>33200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>23200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>31900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>48100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>17600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>29900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>37500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>20800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>18700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>21600</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>20100</v>
       </c>
       <c r="AC26" s="3">
         <v>20100</v>
       </c>
       <c r="AD26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-51100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>15400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E27" s="3">
         <v>24900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>41000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>32900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>33200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>31900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>48100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>17600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>29900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>37500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>20800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>11600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>21600</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>20100</v>
       </c>
       <c r="AC27" s="3">
         <v>20100</v>
       </c>
       <c r="AD27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-51100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>15400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2538,8 +2595,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2591,8 +2651,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>10</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>10</v>
@@ -2609,14 +2669,14 @@
       <c r="Y29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA29" s="3">
         <v>300</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-28100</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>10</v>
@@ -2630,8 +2690,11 @@
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2722,8 +2785,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2814,192 +2880,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>3800</v>
       </c>
       <c r="Q32" s="3">
         <v>3800</v>
       </c>
       <c r="R32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="S32" s="3">
         <v>4100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>800</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>1400</v>
       </c>
       <c r="AC32" s="3">
         <v>1400</v>
       </c>
       <c r="AD32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE32" s="3">
         <v>1700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E33" s="3">
         <v>24900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>41000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>32900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>33200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>31900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>48100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>17600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>29900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>37500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>20800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>11900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>20100</v>
       </c>
       <c r="AC33" s="3">
         <v>20100</v>
       </c>
       <c r="AD33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-51100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>15400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3090,197 +3165,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E35" s="3">
         <v>24900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>41000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>32900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>33200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>31900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>48100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>17600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>29900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>37500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>20800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>11900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>20100</v>
       </c>
       <c r="AC35" s="3">
         <v>20100</v>
       </c>
       <c r="AD35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-51100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>15400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44191</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3313,8 +3397,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3347,100 +3432,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E41" s="3">
         <v>351000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>285700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>284500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>224000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>241200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>214900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>259500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>236900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>192400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>173500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>192300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>189000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>279200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>275700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>137300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>126400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>112000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>190200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>169400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>154900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>199800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>192100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>180200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>251600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>203600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>171700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>139600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>129600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>138900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3531,376 +3620,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>211600</v>
+      </c>
+      <c r="E43" s="3">
         <v>174200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>177100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>179100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>181100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>171500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>146500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>159400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>155000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>141300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>132900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>127600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>146900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>141500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>141100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>165200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>170800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>176500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>163300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>185000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>167600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>161600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>151300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>151200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>146700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>143700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>151500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>152700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>150600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E44" s="3">
         <v>285800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>289200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>259400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>255800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>254700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>277900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>293000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>305700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>322700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>326500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>322600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>299700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>305200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>294500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>270300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>254200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>244500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>222000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>194300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>168900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>163600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>175300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>160800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>158800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>168600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>173900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>176900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>188500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E45" s="3">
         <v>54700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>49600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>46700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>45500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>48400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>31900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>51500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>30800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>31200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>34700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>27400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>24400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>27900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>32200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>29000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>32600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>37500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>30900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>40900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>27900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>765000</v>
+      </c>
+      <c r="E46" s="3">
         <v>865700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>801600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>769700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>706300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>715800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>687800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>756000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>729500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>699200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>684400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>693500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>668300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>760300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>759400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>603600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>582600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>567800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>615300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>576100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>515900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>552800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>551000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>521200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>589700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>553400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>528100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>510000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>496600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>512400</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3991,192 +4095,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>318700</v>
+      </c>
+      <c r="E48" s="3">
         <v>307800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>304500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>310900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>313100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>307800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>288300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>258500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>238800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>223700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>214800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>217600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>240000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>240400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>243000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>305600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>322300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>264200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>276700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>344000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>351100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>344600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>315900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>332200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>330000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>320200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>322000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>323900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>336000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>984300</v>
+      </c>
+      <c r="E49" s="3">
         <v>715900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>734100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>742000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>750500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>757600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>768800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>777500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>792200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>805800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>820000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>831900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>335200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>341800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>354800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>343800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>318400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>324600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>331500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>338500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>345400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>352300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>359600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>368000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>375000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>380500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>384400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>388400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>452700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4267,8 +4380,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4359,100 +4475,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E52" s="3">
         <v>121900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>122100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>112200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>108100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>83900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>75600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>67700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>70900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>72700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>75000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>76900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>74500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>75700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>76000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>33900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>36100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>16200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>15200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16900</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>17000</v>
       </c>
       <c r="AC52" s="3">
         <v>17000</v>
       </c>
       <c r="AD52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AE52" s="3">
         <v>16400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>21200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4543,100 +4665,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2200400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2011300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1962300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1934800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1878100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1865100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1820500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1859700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1831400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1801500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1794200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1819900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1318100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1418200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1433200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1267100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1237700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1190500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1259600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1274800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1227600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1265700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1241200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1237300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1311700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1271200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1251400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1238700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1306400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1334800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4669,8 +4797,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4703,560 +4832,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E57" s="3">
         <v>80200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>78100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>63900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>63800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>61500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>57900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>58400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>51200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>49100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>50300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>49100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>48500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>50700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>52300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>57400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>60800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>63400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>62600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>57900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>65400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>55300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>41500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>41800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>39400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>43000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>48800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>13600</v>
+        <v>13700</v>
       </c>
       <c r="E58" s="3">
         <v>13600</v>
       </c>
       <c r="F58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="G58" s="3">
         <v>11800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>58200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>214100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>144100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>82700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>17000</v>
       </c>
       <c r="N58" s="3">
         <v>17000</v>
       </c>
       <c r="O58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="P58" s="3">
         <v>17100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>167000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>231400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>77000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>62000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>56900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>117500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>27700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>17200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>12700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>17000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>194300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>151500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>108600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>65900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>61000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>66300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>191200</v>
+      </c>
+      <c r="E59" s="3">
         <v>170500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>145200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>176100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>153200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>142500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>115700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>169700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>160200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>160800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>162200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>186200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>134400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>122500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>128000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>147100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>142400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>125700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>115300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>144700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>131500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>118600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>111600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>135200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>131200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>104600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>100300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>107200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>101100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>261800</v>
+      </c>
+      <c r="E60" s="3">
         <v>264200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>236900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>251800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>226900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>262200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>180500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>442300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>355400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>288500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>228300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>253500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>194400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>338600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>407800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>274800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>256700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>240100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>293700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>235800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>211300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>189200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>194000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>384700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>324200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>255000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>205500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>211200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>216200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>856800</v>
+      </c>
+      <c r="E61" s="3">
         <v>748700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>751400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>754100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>756800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>759600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>763100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>559400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>633100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>698000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>767300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>690600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>292700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>297000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>296900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>305500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>309700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>314000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>318100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>322500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>326600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>331000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>330800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>59400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>118700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>178000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>237200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>253600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>270000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>138500</v>
+      </c>
+      <c r="E62" s="3">
         <v>104700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>109300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>110900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>118400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>114400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>106500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>108600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>112100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>116400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>121400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>144200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>111800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>114700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>119900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>99700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>96700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>52700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>56800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>48700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>46600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>44200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>42300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>40800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>46000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>36900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>35900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>34300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>49300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5347,8 +5495,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5439,8 +5590,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5531,100 +5685,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1257100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1117600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1097600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1116800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1102100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1136100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1050100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1110300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1100600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1102900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1117100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1088300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>598900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>750300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>824600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>680000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>663200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>606800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>668600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>606900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>584500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>564400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>567100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>484900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>488900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>469900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>478600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>499100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>535500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>585700</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5657,8 +5817,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5749,8 +5910,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5841,8 +6005,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5933,8 +6100,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6025,100 +6195,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>340100</v>
+      </c>
+      <c r="E72" s="3">
         <v>308900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>284000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>253200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>223800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>204400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>222300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>202400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>192700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>169400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>154600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>158000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>169000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>137100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>89000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>78500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>69900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>85600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>99400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>161400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>140600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>194400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>189900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>266900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>323600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>330200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>310100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>289900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>341100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>325700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6209,8 +6385,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6301,8 +6480,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6393,100 +6575,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>943300</v>
+      </c>
+      <c r="E76" s="3">
         <v>893700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>864600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>818000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>776000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>729000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>770400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>749400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>730800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>698500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>677100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>731700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>719200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>667900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>608600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>587100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>574600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>583800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>591000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>667900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>643100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>701300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>674100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>752400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>822800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>801300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>772800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>739600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>770900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6577,197 +6765,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44191</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E81" s="3">
         <v>24900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>41000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>32900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>33200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>31900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>48100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>17600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>29900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>37500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>20800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>11900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>20100</v>
       </c>
       <c r="AC81" s="3">
         <v>20100</v>
       </c>
       <c r="AD81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-51100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>15400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6800,100 +6997,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>23000</v>
+        <v>23500</v>
       </c>
       <c r="E83" s="3">
         <v>23000</v>
       </c>
       <c r="F83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="G83" s="3">
         <v>23900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>22400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>20700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>28800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>27100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>27000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>27400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>29800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>27900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>25300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>26400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>23000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>22300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>22200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>21800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>22200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>22300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6984,8 +7185,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7076,8 +7280,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7168,8 +7375,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7260,8 +7470,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7352,100 +7565,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>99100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>79600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>64400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>87000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>42000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>68100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>62400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>43500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>66300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>11800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>46400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>79300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>29900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>20600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>58200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>57400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>23100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>57600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>65400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>58900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>38400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>34600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>55200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7478,100 +7697,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-45500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-35100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-29200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-48500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7662,8 +7885,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7754,100 +7980,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-268900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-36500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-34500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-429100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>37100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-45100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>6000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-13200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-27600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-48100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-26300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7880,8 +8112,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7972,8 +8205,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8064,8 +8300,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8156,8 +8395,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8248,280 +8490,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-49700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-25700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-23400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>432800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-149900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-64300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>149000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>11400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-46200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-112500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>16100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-76200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>18700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>1500</v>
       </c>
       <c r="Q101" s="3">
         <v>1500</v>
       </c>
       <c r="R101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S101" s="3">
         <v>-1700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-157000</v>
+      </c>
+      <c r="E102" s="3">
         <v>65300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>60500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-44500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>44500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-90200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>138400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>10900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-78200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>20900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-44900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>7700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>48000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>31900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>32200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>9900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>20600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>HAE</t>
   </si>
@@ -656,423 +656,436 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44191</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>343300</v>
+      </c>
+      <c r="E8" s="3">
         <v>336300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>318200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>311300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>304400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>305300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>297500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>261500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>265000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>259800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>239900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>228500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>225000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>240400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>209500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>195600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>238500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>259000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>252600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>238500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>249300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>247400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>241600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>229300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>233600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>234000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>225400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>211000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>228100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>227800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>163400</v>
+      </c>
+      <c r="E9" s="3">
         <v>151300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>147600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>143900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>148200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>146600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>139600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>119400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>128700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>121400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>117100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>118200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>143100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>120200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>104000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>105000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>124900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>130900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>125600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>122500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>138100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>136200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>129700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>124900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>129200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>122700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>120800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>119300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>146000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>126800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>179900</v>
+      </c>
+      <c r="E10" s="3">
         <v>185000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>170600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>167400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>156200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>158700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>157900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>142100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>136300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>138400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>122800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>110300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>82000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>120200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>105500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>90600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>113600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>128100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>127000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>116000</v>
-      </c>
-      <c r="W10" s="3">
-        <v>111200</v>
       </c>
       <c r="X10" s="3">
         <v>111200</v>
       </c>
       <c r="Y10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="Z10" s="3">
         <v>111900</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>104400</v>
       </c>
       <c r="AA10" s="3">
         <v>104400</v>
       </c>
       <c r="AB10" s="3">
+        <v>104400</v>
+      </c>
+      <c r="AC10" s="3">
         <v>111300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>104600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>91700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>82100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>101000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1106,103 +1119,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E12" s="3">
         <v>12900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12700</v>
-      </c>
-      <c r="I12" s="3">
-        <v>10900</v>
       </c>
       <c r="J12" s="3">
         <v>10900</v>
       </c>
       <c r="K12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="L12" s="3">
         <v>13200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>11100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>12400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>8200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1296,144 +1313,150 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E14" s="3">
         <v>13000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>12800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
-        <v>2200</v>
-      </c>
       <c r="H14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-31600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>51700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>6400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>24500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>31700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>57200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>400</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E15" s="3">
         <v>6900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>32800</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>10</v>
@@ -1447,8 +1470,8 @@
       <c r="T15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1486,8 +1509,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1518,198 +1544,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>313300</v>
+      </c>
+      <c r="E17" s="3">
         <v>290300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>282900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>257700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>269200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>262000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>250800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>230700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>245800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>224100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>215400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>227100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>246200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>199900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>150700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>183900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>212500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>218100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>202800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>251800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>225400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>219000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>215500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>224100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>219300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>233000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>201100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>186300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>285600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>206600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E18" s="3">
         <v>46000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>35300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>53600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>35200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>43300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>46700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>40500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>58800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>26000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>40900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>49800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>23900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>28400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>26100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>24700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-57500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>21200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1743,198 +1776,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-3800</v>
       </c>
       <c r="R20" s="3">
         <v>-3800</v>
       </c>
       <c r="S20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="T20" s="3">
         <v>-4100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-1400</v>
       </c>
       <c r="AD20" s="3">
         <v>-1400</v>
       </c>
       <c r="AE20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E21" s="3">
         <v>67600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>55800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>74600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>56500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>65800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>64500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>47900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>40100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>43500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>25000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>58100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>75800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>28700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>50700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>64900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>72100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>51600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>53400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>48300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>29700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>36300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>22500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>45100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>45000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>41200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1968,11 +2008,11 @@
       <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" s="3">
         <v>3000</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>10</v>
@@ -1989,8 +2029,8 @@
       <c r="T22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2028,198 +2068,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E23" s="3">
         <v>44000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>51600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>32600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>42200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>41100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>19900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-27400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>37400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>55000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>22000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>37800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>45100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-17700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>21800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>25500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>23000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>13300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>22900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>23300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-59200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>18900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="3">
         <v>12800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7900</v>
-      </c>
-      <c r="J24" s="3">
-        <v>5600</v>
       </c>
       <c r="K24" s="3">
         <v>5600</v>
       </c>
       <c r="L24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="M24" s="3">
         <v>8200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-16400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-9200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-21300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2313,198 +2362,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E26" s="3">
         <v>31200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>24900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>41000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>32900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>33200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>48100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>17600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>29900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>37500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>20800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>18300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>11600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>21600</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>20100</v>
       </c>
       <c r="AD26" s="3">
         <v>20100</v>
       </c>
       <c r="AE26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-51100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>15400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E27" s="3">
         <v>31200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>24900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>41000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>32900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>33200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>48100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>17600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>29900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>37500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>20800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>11600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>21600</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>20100</v>
       </c>
       <c r="AD27" s="3">
         <v>20100</v>
       </c>
       <c r="AE27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-51100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>15400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2598,8 +2656,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2654,8 +2715,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>10</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>10</v>
@@ -2672,14 +2733,14 @@
       <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB29" s="3">
         <v>300</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-28100</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
@@ -2693,8 +2754,11 @@
       <c r="AG29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2788,8 +2852,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2883,198 +2950,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>3800</v>
       </c>
       <c r="R32" s="3">
         <v>3800</v>
       </c>
       <c r="S32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="T32" s="3">
         <v>4100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>800</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>1400</v>
       </c>
       <c r="AD32" s="3">
         <v>1400</v>
       </c>
       <c r="AE32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E33" s="3">
         <v>31200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>24900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>41000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>32900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>33200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>31900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>48100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>17600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>29900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>37500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>20800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>11900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>20100</v>
       </c>
       <c r="AD33" s="3">
         <v>20100</v>
       </c>
       <c r="AE33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-51100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>15400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3168,203 +3244,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E35" s="3">
         <v>31200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>24900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>41000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>32900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>33200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>31900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>48100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>17600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>29900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>37500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>20800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>11900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>20100</v>
       </c>
       <c r="AD35" s="3">
         <v>20100</v>
       </c>
       <c r="AE35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-51100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>15400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44191</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3398,8 +3483,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3433,103 +3519,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>178800</v>
+      </c>
+      <c r="E41" s="3">
         <v>194000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>351000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>285700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>284500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>224000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>241200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>214900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>259500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>236900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>192400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>173500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>192300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>189000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>279200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>275700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>137300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>126400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>112000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>190200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>169400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>154900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>199800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>192100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>180200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>251600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>203600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>171700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>139600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>129600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>138900</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3623,388 +3713,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>206600</v>
+      </c>
+      <c r="E43" s="3">
         <v>211600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>174200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>177100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>179100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>181100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>171500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>146500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>159400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>155000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>141300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>132900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>127600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>146900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>141500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>141100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>165200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>170800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>176500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>163300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>185000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>167600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>161600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>151300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>151200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>146700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>143700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>151500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>152700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>150600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>317200</v>
+      </c>
+      <c r="E44" s="3">
         <v>304000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>285800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>289200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>259400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>255800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>254700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>277900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>293000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>305700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>322700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>326500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>322600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>299700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>305200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>294500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>270300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>254200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>244500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>222000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>194300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>168900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>163600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>175300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>160800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>158800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>168600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>173900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>176900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>188500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E45" s="3">
         <v>55400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>54700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>49600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>46700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>45500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>42900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>48100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>30800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>34700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>27400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>24400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>27900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>32200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>32600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>37500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>30900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>40900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>27900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>768900</v>
+      </c>
+      <c r="E46" s="3">
         <v>765000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>865700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>801600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>769700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>706300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>715800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>687800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>756000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>729500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>699200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>684400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>693500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>668300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>760300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>759400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>603600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>582600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>567800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>615300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>576100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>515900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>552800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>551000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>521200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>589700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>553400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>528100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>510000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>496600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>512400</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4098,198 +4203,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>311400</v>
+      </c>
+      <c r="E48" s="3">
         <v>318700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>307800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>304500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>310900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>313100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>307800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>288300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>258500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>238800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>223700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>214800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>217600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>240000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>240400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>243000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>305600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>322300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>264200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>276700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>344000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>351100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>344600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>315900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>332200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>330000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>320200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>322000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>323900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>336000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>971200</v>
+      </c>
+      <c r="E49" s="3">
         <v>984300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>715900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>734100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>742000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>750500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>757600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>768800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>777500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>792200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>805800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>820000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>831900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>335200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>341800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>354800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>343800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>318400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>324600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>331500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>338500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>345400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>352300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>359600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>368000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>375000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>380500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>384400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>388400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>452700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4383,8 +4497,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4478,103 +4595,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>144100</v>
+      </c>
+      <c r="E52" s="3">
         <v>132500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>121900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>122100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>112200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>108100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>83900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>75600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>67700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>70900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>72700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>75000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>76900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>74500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>75700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>76000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>33900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>36100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>16200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>16900</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>17000</v>
       </c>
       <c r="AD52" s="3">
         <v>17000</v>
       </c>
       <c r="AE52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AF52" s="3">
         <v>16400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>21200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4668,103 +4791,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2195600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2200400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2011300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1962300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1934800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1878100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1865100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1820500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1859700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1831400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1801500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1794200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1819900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1318100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1418200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1433200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1267100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1237700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1190500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1259600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1274800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1227600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1265700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1241200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1237300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1311700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1271200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1251400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1238700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1306400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1334800</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4798,8 +4927,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4833,578 +4963,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E57" s="3">
         <v>56800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>80200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>78100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>63900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>63800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>61500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>57900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>58400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>51200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>49100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>50300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>43000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>49100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>48500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>50700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>52300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>57400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>60800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>63400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>62600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>57900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>65400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>55300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>41500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>41800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>39400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>43000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>48800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E58" s="3">
         <v>13700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>13600</v>
       </c>
       <c r="F58" s="3">
         <v>13600</v>
       </c>
       <c r="G58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="H58" s="3">
         <v>11800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>58200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>214100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>144100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>82700</v>
-      </c>
-      <c r="N58" s="3">
-        <v>17000</v>
       </c>
       <c r="O58" s="3">
         <v>17000</v>
       </c>
       <c r="P58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>17100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>167000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>231400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>77000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>62000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>56900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>117500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>27700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>17200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>12700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>17000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>194300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>151500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>108600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>65900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>61000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>66300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E59" s="3">
         <v>191200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>170500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>145200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>176100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>153200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>142500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>115700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>169700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>160200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>160800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>162200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>186200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>134400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>122500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>128000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>147100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>142400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>125700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>115300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>144700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>131500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>118600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>111600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>135200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>131200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>104600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>100300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>107200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>101100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>300400</v>
+      </c>
+      <c r="E60" s="3">
         <v>261800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>264200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>236900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>251800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>226900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>262200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>180500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>442300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>355400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>288500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>228300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>253500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>194400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>338600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>407800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>274800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>256700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>240100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>293700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>235800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>211300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>189200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>194000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>384700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>324200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>255000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>205500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>211200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>216200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>797600</v>
+      </c>
+      <c r="E61" s="3">
         <v>856800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>748700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>751400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>754100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>756800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>759600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>763100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>559400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>633100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>698000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>767300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>690600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>292700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>297000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>296900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>305500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>309700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>314000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>318100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>322500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>326600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>331000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>330800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>59400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>118700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>178000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>237200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>253600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>270000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>137700</v>
+      </c>
+      <c r="E62" s="3">
         <v>138500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>104700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>109300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>110900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>118400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>114400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>106500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>108600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>112100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>116400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>121400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>144200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>111800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>114700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>119900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>99700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>96700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>52700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>56800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>48700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>46600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>44200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>42300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>40800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>46000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>36900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>35900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>34300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>49300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5498,8 +5647,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5593,8 +5745,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5688,103 +5843,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1235600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1257100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1117600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1097600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1116800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1102100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1136100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1050100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1110300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1100600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1102900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1117100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1088300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>598900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>750300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>824600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>680000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>663200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>606800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>668600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>606900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>584500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>564400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>567100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>484900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>488900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>469900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>478600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>499100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>535500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>585700</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5818,8 +5979,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5913,8 +6075,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6008,8 +6173,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6103,8 +6271,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6198,103 +6369,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>360500</v>
+      </c>
+      <c r="E72" s="3">
         <v>340100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>308900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>284000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>253200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>223800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>204400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>222300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>202400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>192700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>169400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>154600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>158000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>169000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>137100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>89000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>78500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>69900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>85600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>99400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>161400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>140600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>194400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>189900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>266900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>323600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>330200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>310100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>289900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>341100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>325700</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6388,8 +6565,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6483,8 +6663,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6578,103 +6761,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>960000</v>
+      </c>
+      <c r="E76" s="3">
         <v>943300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>893700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>864600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>818000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>776000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>729000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>770400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>749400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>730800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>698500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>677100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>731700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>719200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>667900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>608600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>587100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>574600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>583800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>591000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>667900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>643100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>701300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>674100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>752400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>822800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>801300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>772800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>739600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>770900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6768,203 +6957,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44191</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E81" s="3">
         <v>31200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>24900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>41000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>32900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>33200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>31900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>48100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>17600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>29900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>37500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>20800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>11900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>20100</v>
       </c>
       <c r="AD81" s="3">
         <v>20100</v>
       </c>
       <c r="AE81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-51100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>15400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6998,103 +7196,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E83" s="3">
         <v>23500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>23000</v>
       </c>
       <c r="F83" s="3">
         <v>23000</v>
       </c>
       <c r="G83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="H83" s="3">
         <v>23900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>23600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>22400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>21900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>20900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>20700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>28800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>27100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>27000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>27400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>29800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>27900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>25300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>26400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>23000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>22300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>22200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>21800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>22200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7188,8 +7390,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7283,8 +7488,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7378,8 +7586,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7473,8 +7684,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7568,103 +7782,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>99100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>19100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>79600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>64400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>87000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>42000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>68100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>62400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>66300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>29200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>46400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>79300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>29900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>20600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>58200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>57400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>23100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>57600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>65400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>58900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>38400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>34600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>55200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7698,103 +7918,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-45500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-35100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-29200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-48500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7888,8 +8112,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7983,103 +8210,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-268900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-25100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-18000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-36500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-31100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-58200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-20500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-429100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>37100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-23900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-45100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>6000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-13200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-27600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-48100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-26300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8113,8 +8346,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8208,8 +8442,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8303,8 +8540,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8398,8 +8638,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8493,289 +8736,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="E100" s="3">
         <v>109400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-49700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-23400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>432800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-149900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-64300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>149000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>11400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-46200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-112500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>16100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>7000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-76200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>18700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>8300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>1500</v>
       </c>
       <c r="R101" s="3">
         <v>1500</v>
       </c>
       <c r="S101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T101" s="3">
         <v>-1700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-157000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>65300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>60500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-44500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>22600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>44500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-90200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>138400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>10900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>14400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-78200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>20900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>14500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-44900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>7700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>48000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>31900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>32200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>9900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>20600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>HAE</t>
   </si>
@@ -656,436 +656,449 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44191</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>336200</v>
+      </c>
+      <c r="E8" s="3">
         <v>343300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>336300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>318200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>311300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>304400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>305300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>297500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>261500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>265000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>259800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>239900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>228500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>225000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>240400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>209500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>195600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>238500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>259000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>252600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>238500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>249300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>247400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>241600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>229300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>233600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>234000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>225400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>211000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>228100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>227800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>156900</v>
+      </c>
+      <c r="E9" s="3">
         <v>163400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>151300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>147600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>143900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>148200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>146600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>139600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>119400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>128700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>121400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>117100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>118200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>143100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>120200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>104000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>105000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>124900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>130900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>125600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>122500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>138100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>136200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>129700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>124900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>129200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>122700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>120800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>119300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>146000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>126800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>179300</v>
+      </c>
+      <c r="E10" s="3">
         <v>179900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>185000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>170600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>167400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>156200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>158700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>157900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>142100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>136300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>138400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>122800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>110300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>82000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>120200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>105500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>90600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>113600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>128100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>127000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>116000</v>
-      </c>
-      <c r="X10" s="3">
-        <v>111200</v>
       </c>
       <c r="Y10" s="3">
         <v>111200</v>
       </c>
       <c r="Z10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="AA10" s="3">
         <v>111900</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>104400</v>
       </c>
       <c r="AB10" s="3">
         <v>104400</v>
       </c>
       <c r="AC10" s="3">
+        <v>104400</v>
+      </c>
+      <c r="AD10" s="3">
         <v>111300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>104600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>91700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>82100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>101000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1120,106 +1133,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E12" s="3">
         <v>15700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>10900</v>
       </c>
       <c r="K12" s="3">
         <v>10900</v>
       </c>
       <c r="L12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="M12" s="3">
         <v>13200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>11100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>12400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>8200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1316,150 +1333,156 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E14" s="3">
         <v>12000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>13000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>16600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-31600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>10300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>51700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>6400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>24500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>31700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>57200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>400</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E15" s="3">
         <v>10400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>32800</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>10</v>
@@ -1473,8 +1496,8 @@
       <c r="U15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1512,8 +1535,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1545,204 +1571,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>296400</v>
+      </c>
+      <c r="E17" s="3">
         <v>313300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>290300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>282900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>257700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>269200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>262000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>250800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>230700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>245800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>224100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>215400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>227100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>246200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>199900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>150700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>183900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>212500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>218100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>202800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>251800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>225400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>219000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>215500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>224100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>219300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>233000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>201100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>186300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>285600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>206600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E18" s="3">
         <v>30000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>35300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>53600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>35200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>43300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>46700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>30800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>35700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>24500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>40500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>58800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>26000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>40900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>49800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-13300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>23900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>28400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>26100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>24300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>24700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-57500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>21200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1777,204 +1810,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-3800</v>
       </c>
       <c r="S20" s="3">
         <v>-3800</v>
       </c>
       <c r="T20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="U20" s="3">
         <v>-4100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-1400</v>
       </c>
       <c r="AE20" s="3">
         <v>-1400</v>
       </c>
       <c r="AF20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>75800</v>
+      </c>
+      <c r="E21" s="3">
         <v>51100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>67600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>55800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>74600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>56500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>65800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>64500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>47900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>40100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>55800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>43500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>25000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>58100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>75800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>50700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>64900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>72100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>51600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>53400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>48300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>29700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>36300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>22500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>45100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>45000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>41200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2011,11 +2051,11 @@
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="3">
         <v>3000</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>10</v>
@@ -2032,8 +2072,8 @@
       <c r="U22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2071,204 +2111,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E23" s="3">
         <v>23400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>44000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>32800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>51600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>32600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>42200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>41100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>25500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>19900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>37400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>55000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>22000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>37800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>45100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-17700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>21800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>25500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>23000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>13300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>22900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>23300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-59200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>18900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E24" s="3">
         <v>3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7900</v>
-      </c>
-      <c r="K24" s="3">
-        <v>5600</v>
       </c>
       <c r="L24" s="3">
         <v>5600</v>
       </c>
       <c r="M24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N24" s="3">
         <v>8200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-9200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-21300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2365,204 +2414,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E26" s="3">
         <v>20400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>41000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>29400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>32900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>33200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>31900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>48100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>17600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>29900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>37500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>20800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>18300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>11600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>21600</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>20100</v>
       </c>
       <c r="AE26" s="3">
         <v>20100</v>
       </c>
       <c r="AF26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AG26" s="3">
         <v>-51100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>15400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E27" s="3">
         <v>20400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>31200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>41000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>29400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>32900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>33200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>48100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>17600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>29900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>37500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>20800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>11600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>21600</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>20100</v>
       </c>
       <c r="AE27" s="3">
         <v>20100</v>
       </c>
       <c r="AF27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>-51100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>15400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2659,8 +2717,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2718,8 +2779,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>10</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>10</v>
@@ -2736,14 +2797,14 @@
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="3">
         <v>300</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-28100</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>10</v>
@@ -2757,8 +2818,11 @@
       <c r="AH29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2855,8 +2919,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2953,204 +3020,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E32" s="3">
         <v>6500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>3800</v>
       </c>
       <c r="S32" s="3">
         <v>3800</v>
       </c>
       <c r="T32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U32" s="3">
         <v>4100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>1400</v>
       </c>
       <c r="AE32" s="3">
         <v>1400</v>
       </c>
       <c r="AF32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AG32" s="3">
         <v>1700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E33" s="3">
         <v>20400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>41000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>29400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>32900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>33200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>31900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>48100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>17600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>29900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>37500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>20800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>11900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>20100</v>
       </c>
       <c r="AE33" s="3">
         <v>20100</v>
       </c>
       <c r="AF33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>-51100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>15400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3247,209 +3323,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E35" s="3">
         <v>20400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>41000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>29400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>32900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>33200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>31900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>48100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>17600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>29900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>37500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>20800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>11900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>20100</v>
       </c>
       <c r="AE35" s="3">
         <v>20100</v>
       </c>
       <c r="AF35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>-51100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>15400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44191</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3484,8 +3569,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3520,106 +3606,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>344400</v>
+      </c>
+      <c r="E41" s="3">
         <v>178800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>194000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>351000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>285700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>284500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>224000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>241200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>214900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>259500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>236900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>192400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>173500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>192300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>189000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>279200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>275700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>137300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>126400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>112000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>190200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>169400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>154900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>199800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>192100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>180200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>251600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>203600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>171700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>139600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>129600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>138900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3716,400 +3806,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>201500</v>
+      </c>
+      <c r="E43" s="3">
         <v>206600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>211600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>174200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>177100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>179100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>181100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>171500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>146500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>159400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>155000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>141300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>132900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>127600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>146900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>141500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>141100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>165200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>170800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>176500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>163300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>185000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>167600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>161600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>151300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>151200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>146700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>143700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>151500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>152700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>150600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>373800</v>
+      </c>
+      <c r="E44" s="3">
         <v>317200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>304000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>285800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>289200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>259400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>255800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>254700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>277900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>293000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>305700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>322700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>326500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>322600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>299700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>305200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>294500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>270300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>254200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>244500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>222000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>194300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>168900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>163600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>175300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>160800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>158800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>168600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>173900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>176900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>188500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E45" s="3">
         <v>66300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>55400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>54700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>49600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>46700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>45500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>48400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>42900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>34400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>48100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>30800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>31200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>34700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>39800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>27400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>24400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>27900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>32200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>29000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>32600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>37500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>30900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>40900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>27900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>978600</v>
+      </c>
+      <c r="E46" s="3">
         <v>768900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>765000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>865700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>801600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>769700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>706300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>715800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>687800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>756000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>729500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>699200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>684400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>693500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>668300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>760300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>759400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>603600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>582600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>567800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>615300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>576100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>515900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>552800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>551000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>521200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>589700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>553400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>528100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>510000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>496600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>512400</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4206,204 +4311,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>302500</v>
+      </c>
+      <c r="E48" s="3">
         <v>311400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>318700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>307800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>304500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>310900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>313100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>307800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>288300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>258500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>238800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>223700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>214800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>217600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>240000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>240400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>243000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>305600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>322300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>264200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>276700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>344000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>351100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>344600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>315900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>332200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>330000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>320200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>322000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>323900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>336000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1108300</v>
+      </c>
+      <c r="E49" s="3">
         <v>971200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>984300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>715900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>734100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>742000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>750500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>757600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>768800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>777500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>792200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>805800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>820000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>831900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>335200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>341800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>354800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>343800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>318400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>324600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>331500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>338500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>345400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>352300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>359600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>368000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>375000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>380500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>384400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>388400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>452700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4500,8 +4614,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4598,106 +4715,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>151600</v>
+      </c>
+      <c r="E52" s="3">
         <v>144100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>132500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>121900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>122100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>112200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>108100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>83900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>75600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>67700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>70900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>72700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>75000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>76900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>74500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>75700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>76000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>14100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>14500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>33900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>36100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>16200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>15200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>16000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>16900</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>17000</v>
       </c>
       <c r="AE52" s="3">
         <v>17000</v>
       </c>
       <c r="AF52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AG52" s="3">
         <v>16400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>21200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4794,106 +4917,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2541000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2195600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2200400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2011300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1962300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1934800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1878100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1865100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1820500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1859700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1831400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1801500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1794200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1819900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1318100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1418200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1433200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1267100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1237700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1190500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1259600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1274800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1227600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1265700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1241200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1237300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1311700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1271200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1251400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1238700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1306400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1334800</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4928,8 +5057,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4964,596 +5094,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E57" s="3">
         <v>73400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>56800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>80200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>78100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>63900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>63800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>61500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>57900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>58400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>51200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>49100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>50300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>43000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>49100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>48500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>50700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>52300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>57400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>60800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>63400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>62600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>57900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>65400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>55300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>41500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>41800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>39400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>43000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>48800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E58" s="3">
         <v>10200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>13700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>13600</v>
       </c>
       <c r="G58" s="3">
         <v>13600</v>
       </c>
       <c r="H58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="I58" s="3">
         <v>11800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>58200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>214100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>144100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>82700</v>
-      </c>
-      <c r="O58" s="3">
-        <v>17000</v>
       </c>
       <c r="P58" s="3">
         <v>17000</v>
       </c>
       <c r="Q58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="R58" s="3">
         <v>17100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>167000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>231400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>77000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>62000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>56900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>117500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>27700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>17200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>12700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>17000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>194300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>151500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>108600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>65900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>61000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>66300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E59" s="3">
         <v>216800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>191200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>170500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>145200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>176100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>153200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>142500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>115700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>169700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>160200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>160800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>162200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>186200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>134400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>122500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>128000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>147100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>142400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>125700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>115300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>144700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>131500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>118600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>111600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>135200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>131200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>104600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>100300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>107200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>101100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>260100</v>
+      </c>
+      <c r="E60" s="3">
         <v>300400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>261800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>264200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>236900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>251800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>226900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>262200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>180500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>442300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>355400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>288500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>228300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>253500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>194400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>338600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>407800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>274800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>256700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>240100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>293700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>235800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>211300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>189200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>194000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>384700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>324200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>255000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>205500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>211200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>216200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1218500</v>
+      </c>
+      <c r="E61" s="3">
         <v>797600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>856800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>748700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>751400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>754100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>756800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>759600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>763100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>559400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>633100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>698000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>767300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>690600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>292700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>297000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>296900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>305500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>309700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>314000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>318100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>322500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>326600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>331000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>330800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>59400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>118700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>178000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>237200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>253600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>270000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>157100</v>
+      </c>
+      <c r="E62" s="3">
         <v>137700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>138500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>104700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>109300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>110900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>118400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>114400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>106500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>108600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>112100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>116400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>121400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>144200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>111800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>114700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>119900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>99700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>96700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>52700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>56800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>48700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>46600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>44200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>42300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>40800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>46000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>36900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>35900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>34300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>49300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5650,8 +5799,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5748,8 +5900,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5846,106 +6001,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1635600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1235600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1257100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1117600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1097600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1116800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1102100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1136100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1050100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1110300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1100600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1102900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1117100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1088300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>598900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>750300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>824600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>680000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>663200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>606800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>668600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>606900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>584500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>564400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>567100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>484900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>488900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>469900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>478600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>499100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>535500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>585700</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5980,8 +6141,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6078,8 +6240,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6176,8 +6341,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6274,8 +6442,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6372,106 +6543,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>386600</v>
+      </c>
+      <c r="E72" s="3">
         <v>360500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>340100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>308900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>284000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>253200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>223800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>204400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>222300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>202400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>192700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>169400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>154600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>158000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>169000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>137100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>89000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>78500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>69900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>85600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>99400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>161400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>140600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>194400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>189900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>266900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>323600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>330200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>310100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>289900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>341100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>325700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6568,8 +6745,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6666,8 +6846,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6764,106 +6947,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>905400</v>
+      </c>
+      <c r="E76" s="3">
         <v>960000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>943300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>893700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>864600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>818000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>776000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>729000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>770400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>749400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>730800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>698500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>677100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>731700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>719200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>667900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>608600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>587100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>574600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>583800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>591000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>667900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>643100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>701300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>674100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>752400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>822800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>801300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>772800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>739600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>770900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6960,209 +7149,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44191</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E81" s="3">
         <v>20400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>41000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>29400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>32900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>33200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>31900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>48100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>17600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>29900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>37500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>20800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>11900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>20100</v>
       </c>
       <c r="AE81" s="3">
         <v>20100</v>
       </c>
       <c r="AF81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>-51100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>15400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7197,106 +7395,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E83" s="3">
         <v>27600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>23500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>23000</v>
       </c>
       <c r="G83" s="3">
         <v>23000</v>
       </c>
       <c r="H83" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I83" s="3">
         <v>23900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>22400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>21900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>20800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>20900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>28800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>27100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>27000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>27400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>29800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>27900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>25300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>26400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>23000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>22300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>22200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>21800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>22300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7393,8 +7595,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7491,8 +7696,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7589,8 +7797,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7687,8 +7898,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7785,106 +7999,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="E89" s="3">
         <v>64100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>99100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>19100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>79600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>64400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>87000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>42000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>68100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>62400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>66300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>29200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>46400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>79300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>29900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>20600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>58200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>57400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>23100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>57600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>65400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>58900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>38400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>34600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>55200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7919,106 +8139,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-24700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-45500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-35100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-8200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-29200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-48500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8115,8 +8339,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8213,106 +8440,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-139200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-268900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-25100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-58200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-34500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-20500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-429100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>37100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-23900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-45100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>6000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-27600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-26300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-14600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8347,8 +8580,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8445,8 +8679,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8543,8 +8780,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8641,8 +8881,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8739,298 +8982,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>333700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-63500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>109400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-49700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-23400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>432800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-149900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-64300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>149000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>11400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-46200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-112500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>16100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>7000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-76200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>18700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>8300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-12700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-10400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3100</v>
-      </c>
-      <c r="R101" s="3">
-        <v>1500</v>
       </c>
       <c r="S101" s="3">
         <v>1500</v>
       </c>
       <c r="T101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U101" s="3">
         <v>-1700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>165600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-157000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>65300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>60500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>26300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-44500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>22600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>44500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-18800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-90200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>138400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>10900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-78200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>20900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-44900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>7700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>48000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>31900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>32200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>9900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>20600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>HAE</t>
   </si>
@@ -656,449 +656,462 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44562</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44191</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>345500</v>
+      </c>
+      <c r="E8" s="3">
         <v>336200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>343300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>336300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>318200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>311300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>304400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>305300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>297500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>261500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>265000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>259800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>239900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>228500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>225000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>240400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>209500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>195600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>238500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>259000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>252600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>238500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>249300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>247400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>241600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>229300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>233600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>234000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>225400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>211000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>228100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>227800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>156900</v>
+        <v>154300</v>
       </c>
       <c r="E9" s="3">
-        <v>163400</v>
+        <v>151600</v>
       </c>
       <c r="F9" s="3">
+        <v>154300</v>
+      </c>
+      <c r="G9" s="3">
         <v>151300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>147600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>143900</v>
       </c>
-      <c r="I9" s="3">
-        <v>148200</v>
-      </c>
       <c r="J9" s="3">
+        <v>140200</v>
+      </c>
+      <c r="K9" s="3">
         <v>146600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>139600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>119400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>128700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>121400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>117100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>118200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>143100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>120200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>104000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>105000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>124900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>130900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>125600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>122500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>138100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>136200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>129700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>124900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>129200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>122700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>120800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>119300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>146000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>126800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>179300</v>
+        <v>191200</v>
       </c>
       <c r="E10" s="3">
-        <v>179900</v>
+        <v>184500</v>
       </c>
       <c r="F10" s="3">
-        <v>185000</v>
+        <v>188900</v>
       </c>
       <c r="G10" s="3">
+        <v>184900</v>
+      </c>
+      <c r="H10" s="3">
         <v>170600</v>
       </c>
-      <c r="H10" s="3">
-        <v>167400</v>
-      </c>
       <c r="I10" s="3">
-        <v>156200</v>
+        <v>167500</v>
       </c>
       <c r="J10" s="3">
+        <v>164300</v>
+      </c>
+      <c r="K10" s="3">
         <v>158700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>157900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>142100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>136300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>138400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>122800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>110300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>82000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>120200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>105500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>90600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>113600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>128100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>127000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>116000</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>111200</v>
       </c>
       <c r="Z10" s="3">
         <v>111200</v>
       </c>
       <c r="AA10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="AB10" s="3">
         <v>111900</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>104400</v>
       </c>
       <c r="AC10" s="3">
         <v>104400</v>
       </c>
       <c r="AD10" s="3">
+        <v>104400</v>
+      </c>
+      <c r="AE10" s="3">
         <v>111300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>104600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>91700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>82100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>101000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1134,109 +1147,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>14500</v>
+        <v>16500</v>
       </c>
       <c r="E12" s="3">
-        <v>15700</v>
+        <v>14400</v>
       </c>
       <c r="F12" s="3">
+        <v>14000</v>
+      </c>
+      <c r="G12" s="3">
         <v>12900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12600</v>
       </c>
-      <c r="I12" s="3">
-        <v>15600</v>
-      </c>
       <c r="J12" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K12" s="3">
         <v>12700</v>
-      </c>
-      <c r="K12" s="3">
-        <v>10900</v>
       </c>
       <c r="L12" s="3">
         <v>10900</v>
       </c>
       <c r="M12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="N12" s="3">
         <v>13200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>11100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>12400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>8500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1336,156 +1353,162 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>16900</v>
+        <v>6000</v>
       </c>
       <c r="E14" s="3">
-        <v>12000</v>
+        <v>26300</v>
       </c>
       <c r="F14" s="3">
-        <v>13000</v>
+        <v>23500</v>
       </c>
       <c r="G14" s="3">
-        <v>12800</v>
+        <v>8000</v>
       </c>
       <c r="H14" s="3">
-        <v>1000</v>
+        <v>7300</v>
       </c>
       <c r="I14" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-31600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>10300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>51700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>6400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>24500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>31700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>57200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>400</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E15" s="3">
         <v>12500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>32800</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>10</v>
@@ -1499,8 +1522,8 @@
       <c r="V15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1538,8 +1561,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1572,210 +1598,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>296400</v>
+        <v>287800</v>
       </c>
       <c r="E17" s="3">
-        <v>313300</v>
+        <v>270100</v>
       </c>
       <c r="F17" s="3">
-        <v>290300</v>
+        <v>289900</v>
       </c>
       <c r="G17" s="3">
-        <v>282900</v>
+        <v>282300</v>
       </c>
       <c r="H17" s="3">
+        <v>275600</v>
+      </c>
+      <c r="I17" s="3">
         <v>257700</v>
       </c>
-      <c r="I17" s="3">
-        <v>269200</v>
-      </c>
       <c r="J17" s="3">
+        <v>258200</v>
+      </c>
+      <c r="K17" s="3">
         <v>262000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>250800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>230700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>245800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>224100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>215400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>227100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>246200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>199900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>150700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>183900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>212500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>218100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>202800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>251800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>225400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>219000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>215500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>224100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>219300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>233000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>201100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>186300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>285600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>206600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>39800</v>
+        <v>57700</v>
       </c>
       <c r="E18" s="3">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="F18" s="3">
-        <v>46000</v>
+        <v>53400</v>
       </c>
       <c r="G18" s="3">
-        <v>35300</v>
+        <v>53900</v>
       </c>
       <c r="H18" s="3">
+        <v>42600</v>
+      </c>
+      <c r="I18" s="3">
         <v>53600</v>
       </c>
-      <c r="I18" s="3">
-        <v>35200</v>
-      </c>
       <c r="J18" s="3">
+        <v>46300</v>
+      </c>
+      <c r="K18" s="3">
         <v>43300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>46700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>30800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>35700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>24500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>40500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>58800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>26000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>40900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>49800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>23900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>28400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>26100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>24300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>24700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-57500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>21200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1811,233 +1844,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>6900</v>
+      <c r="D20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E20" s="3">
-        <v>-6500</v>
+        <v>-7000</v>
       </c>
       <c r="F20" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2000</v>
+        <v>-5100</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I20" s="3">
-        <v>-2600</v>
+        <v>2100</v>
       </c>
       <c r="J20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-6200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-3800</v>
       </c>
       <c r="T20" s="3">
         <v>-3800</v>
       </c>
       <c r="U20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="V20" s="3">
         <v>-4100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-1400</v>
       </c>
       <c r="AF20" s="3">
         <v>-1400</v>
       </c>
       <c r="AG20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>85500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>69000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>60900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>49800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>59100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>52600</v>
+      </c>
+      <c r="K21" s="3">
+        <v>65800</v>
+      </c>
+      <c r="L21" s="3">
+        <v>64500</v>
+      </c>
+      <c r="M21" s="3">
+        <v>47900</v>
+      </c>
+      <c r="N21" s="3">
+        <v>40100</v>
+      </c>
+      <c r="O21" s="3">
+        <v>55800</v>
+      </c>
+      <c r="P21" s="3">
+        <v>43500</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>25000</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="S21" s="3">
+        <v>58100</v>
+      </c>
+      <c r="T21" s="3">
         <v>75800</v>
       </c>
-      <c r="E21" s="3">
-        <v>51100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>67600</v>
-      </c>
-      <c r="G21" s="3">
-        <v>55800</v>
-      </c>
-      <c r="H21" s="3">
-        <v>74600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>56500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>65800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>64500</v>
-      </c>
-      <c r="L21" s="3">
-        <v>47900</v>
-      </c>
-      <c r="M21" s="3">
-        <v>40100</v>
-      </c>
-      <c r="N21" s="3">
-        <v>55800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>43500</v>
-      </c>
-      <c r="P21" s="3">
-        <v>25000</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="R21" s="3">
-        <v>58100</v>
-      </c>
-      <c r="S21" s="3">
-        <v>75800</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>28700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>50700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>64900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>72100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>51600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>53400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>48300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>29700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>36300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>22500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>45100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>45000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>41200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+      <c r="D22" s="3">
+        <v>7000</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="3">
+        <v>11600</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2500</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>10</v>
+      <c r="J22" s="3">
+        <v>1000</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>10</v>
@@ -2054,11 +2094,11 @@
       <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="3">
         <v>3000</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>10</v>
@@ -2075,8 +2115,8 @@
       <c r="V22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2114,210 +2154,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E23" s="3">
         <v>46700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>23400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>44000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>32800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>51600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>42200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>41100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>31400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>19900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>37400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>55000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>22000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>37800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>45100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-17700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>21800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>25500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>23000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>13300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>22900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>23300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-59200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>18900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E24" s="3">
         <v>8300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7900</v>
-      </c>
-      <c r="L24" s="3">
-        <v>5600</v>
       </c>
       <c r="M24" s="3">
         <v>5600</v>
       </c>
       <c r="N24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="O24" s="3">
         <v>8200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-16400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-21300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2417,210 +2466,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E26" s="3">
         <v>38400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>31200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>24900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>41000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>29400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>32900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>33200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>23200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-11000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>48100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>17600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>29900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>37500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>20800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>18300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>18700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>11600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>21600</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>20100</v>
       </c>
       <c r="AF26" s="3">
         <v>20100</v>
       </c>
       <c r="AG26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-51100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>15400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E27" s="3">
         <v>38400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>31200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>41000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>29400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>32900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>33200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-11000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>48100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>17600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>29900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>37500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>20800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>18700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>11600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>21600</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>20100</v>
       </c>
       <c r="AF27" s="3">
         <v>20100</v>
       </c>
       <c r="AG27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-51100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>15400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2720,8 +2778,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2782,8 +2843,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>10</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>10</v>
@@ -2800,14 +2861,14 @@
       <c r="AB29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="3">
         <v>300</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-28100</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>10</v>
@@ -2821,8 +2882,11 @@
       <c r="AI29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2922,8 +2986,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3023,210 +3090,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-6900</v>
+      <c r="D32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E32" s="3">
-        <v>6500</v>
+        <v>7000</v>
       </c>
       <c r="F32" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2000</v>
+        <v>5100</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="I32" s="3">
-        <v>2600</v>
+        <v>-2100</v>
       </c>
       <c r="J32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>6200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>3800</v>
       </c>
       <c r="T32" s="3">
         <v>3800</v>
       </c>
       <c r="U32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="V32" s="3">
         <v>4100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>800</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>1400</v>
       </c>
       <c r="AF32" s="3">
         <v>1400</v>
       </c>
       <c r="AG32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AH32" s="3">
         <v>1700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E33" s="3">
         <v>38400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>31200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>41000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>29400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>32900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>33200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>23200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>48100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>17600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>29900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>37500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>20800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>18700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>11900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>20100</v>
       </c>
       <c r="AF33" s="3">
         <v>20100</v>
       </c>
       <c r="AG33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-51100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>15400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3326,215 +3402,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E35" s="3">
         <v>38400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>31200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>41000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>29400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>32900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>33200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>23200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>48100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>17600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>29900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>37500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>20800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>18700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>11900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>20100</v>
       </c>
       <c r="AF35" s="3">
         <v>20100</v>
       </c>
       <c r="AG35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-51100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>15400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44562</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44191</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3570,8 +3655,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3607,132 +3693,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>299300</v>
+      </c>
+      <c r="E41" s="3">
         <v>344400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>178800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>194000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>351000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>285700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>284500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>224000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>241200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>214900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>259500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>236900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>192400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>173500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>192300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>189000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>279200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>275700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>137300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>126400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>112000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>190200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>169400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>154900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>199800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>192100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>180200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>251600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>203600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>171700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>139600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>129600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>138900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3809,435 +3899,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>213500</v>
+      </c>
+      <c r="E43" s="3">
         <v>201500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>206600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>211600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>174200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>177100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>179100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>181100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>171500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>146500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>159400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>155000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>141300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>132900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>127600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>146900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>141500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>141100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>165200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>170800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>176500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>163300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>185000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>167600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>161600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>151300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>151200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>146700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>143700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>151500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>152700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>150600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>382100</v>
+      </c>
+      <c r="E44" s="3">
         <v>373800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>317200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>304000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>285800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>289200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>259400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>255800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>254700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>277900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>293000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>305700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>322700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>326500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>322600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>299700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>305200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>294500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>270300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>254200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>244500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>222000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>194300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>168900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>163600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>175300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>160800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>158800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>168600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>173900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>176900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>188500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>58900</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>66300</v>
+        <v>1900</v>
       </c>
       <c r="F45" s="3">
-        <v>55400</v>
+        <v>1500</v>
       </c>
       <c r="G45" s="3">
-        <v>54700</v>
+        <v>800</v>
       </c>
       <c r="H45" s="3">
-        <v>49600</v>
+        <v>3000</v>
       </c>
       <c r="I45" s="3">
-        <v>46700</v>
+        <v>2600</v>
       </c>
       <c r="J45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K45" s="3">
         <v>45500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>48500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>44100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>42900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>51100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>32700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>34400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>48100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>30800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>31200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>34700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>39800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>27400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>24400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>27900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>32200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>29000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>32600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>37500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>30900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>40900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>27900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>955900</v>
+      </c>
+      <c r="E46" s="3">
         <v>978600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>768900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>765000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>865700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>801600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>769700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>706300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>715800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>687800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>756000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>729500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>699200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>684400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>693500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>668300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>760300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>759400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>603600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>582600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>567800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>615300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>576100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>515900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>552800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>551000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>521200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>589700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>553400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>528100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>510000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>496600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>512400</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4314,210 +4419,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300500</v>
+      </c>
+      <c r="E48" s="3">
         <v>302500</v>
       </c>
-      <c r="E48" s="3">
-        <v>311400</v>
-      </c>
       <c r="F48" s="3">
+        <v>366600</v>
+      </c>
+      <c r="G48" s="3">
         <v>318700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>307800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>304500</v>
       </c>
-      <c r="I48" s="3">
-        <v>310900</v>
-      </c>
       <c r="J48" s="3">
+        <v>364300</v>
+      </c>
+      <c r="K48" s="3">
         <v>313100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>307800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>288300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>258500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>238800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>223700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>214800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>217600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>240000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>240400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>243000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>305600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>322300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>264200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>276700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>344000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>351100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>344600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>315900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>332200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>330000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>320200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>322000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>323900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>336000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1104000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1108300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>971200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>984300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>715900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>734100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>742000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>750500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>757600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>768800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>777500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>792200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>805800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>820000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>831900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>335200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>341800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>354800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>343800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>318400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>324600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>331500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>338500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>345400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>352300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>359600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>368000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>375000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>380500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>384400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>388400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>452700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4617,8 +4731,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4718,109 +4835,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>151600</v>
+        <v>155800</v>
       </c>
       <c r="E52" s="3">
-        <v>144100</v>
+        <v>134700</v>
       </c>
       <c r="F52" s="3">
-        <v>132500</v>
+        <v>81100</v>
       </c>
       <c r="G52" s="3">
-        <v>121900</v>
+        <v>127400</v>
       </c>
       <c r="H52" s="3">
-        <v>122100</v>
+        <v>116600</v>
       </c>
       <c r="I52" s="3">
-        <v>112200</v>
+        <v>117300</v>
       </c>
       <c r="J52" s="3">
+        <v>53600</v>
+      </c>
+      <c r="K52" s="3">
         <v>108100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>83900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>75600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>67700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>70900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>72700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>75000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>76900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>74500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>75700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>76000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>14100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>33900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>36100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>16200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>15200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>14600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>16000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16900</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>17000</v>
       </c>
       <c r="AF52" s="3">
         <v>17000</v>
       </c>
       <c r="AG52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AH52" s="3">
         <v>16400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>21200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4920,109 +5043,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2525200</v>
+      </c>
+      <c r="E54" s="3">
         <v>2541000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2195600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2200400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2011300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1962300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1934800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1878100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1865100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1820500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1859700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1831400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1801500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1794200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1819900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1318100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1418200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1433200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1267100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1237700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1190500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1259600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1274800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1227600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1265700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1241200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1237300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1311700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1271200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1251400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1238700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1306400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1334800</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5058,8 +5187,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5095,614 +5225,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E57" s="3">
         <v>76900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>73400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>80200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>78100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>63900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>63800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>61500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>57900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>58400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>51200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>45000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>49100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>50300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>43000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>49100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>48500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>50700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>52300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>57400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>60800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>63400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>62600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>57900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>65400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>55300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>41500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>41800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>39400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>43000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>48800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E58" s="3">
         <v>5100</v>
       </c>
-      <c r="E58" s="3">
-        <v>10200</v>
-      </c>
       <c r="F58" s="3">
+        <v>18400</v>
+      </c>
+      <c r="G58" s="3">
         <v>13700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>13600</v>
       </c>
       <c r="H58" s="3">
         <v>13600</v>
       </c>
       <c r="I58" s="3">
-        <v>11800</v>
+        <v>13600</v>
       </c>
       <c r="J58" s="3">
+        <v>18900</v>
+      </c>
+      <c r="K58" s="3">
         <v>9900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>58200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>214100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>144100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>82700</v>
-      </c>
-      <c r="P58" s="3">
-        <v>17000</v>
       </c>
       <c r="Q58" s="3">
         <v>17000</v>
       </c>
       <c r="R58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="S58" s="3">
         <v>17100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>167000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>231400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>77000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>62000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>56900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>117500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>27700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>17200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>12700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>17000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>194300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>151500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>108600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>65900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>61000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>66300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>178000</v>
+        <v>150000</v>
       </c>
       <c r="E59" s="3">
-        <v>216800</v>
+        <v>137300</v>
       </c>
       <c r="F59" s="3">
-        <v>191200</v>
+        <v>128000</v>
       </c>
       <c r="G59" s="3">
-        <v>170500</v>
+        <v>132400</v>
       </c>
       <c r="H59" s="3">
-        <v>145200</v>
+        <v>124900</v>
       </c>
       <c r="I59" s="3">
-        <v>176100</v>
+        <v>112300</v>
       </c>
       <c r="J59" s="3">
+        <v>104500</v>
+      </c>
+      <c r="K59" s="3">
         <v>153200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>142500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>115700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>169700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>160200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>160800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>162200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>186200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>134400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>122500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>128000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>147100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>142400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>125700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>115300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>144700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>131500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>118600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>111600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>135200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>131200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>104600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>100300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>107200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>101100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>273900</v>
+      </c>
+      <c r="E60" s="3">
         <v>260100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>300400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>261800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>264200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>236900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>251800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>226900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>262200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>180500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>442300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>355400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>288500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>228300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>253500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>194400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>338600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>407800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>274800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>256700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>240100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>293700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>235800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>211300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>189200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>194000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>384700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>324200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>255000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>205500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>211200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>216200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1218500</v>
+        <v>1309500</v>
       </c>
       <c r="E61" s="3">
-        <v>797600</v>
+        <v>1291600</v>
       </c>
       <c r="F61" s="3">
-        <v>856800</v>
+        <v>855500</v>
       </c>
       <c r="G61" s="3">
+        <v>857300</v>
+      </c>
+      <c r="H61" s="3">
         <v>748700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>751400</v>
       </c>
-      <c r="I61" s="3">
-        <v>754100</v>
-      </c>
       <c r="J61" s="3">
+        <v>811800</v>
+      </c>
+      <c r="K61" s="3">
         <v>756800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>759600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>763100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>559400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>633100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>698000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>767300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>690600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>292700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>297000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>296900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>305500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>309700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>314000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>318100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>322500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>326600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>331000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>330800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>59400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>118700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>178000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>237200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>253600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>270000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>157100</v>
+      <c r="D62" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E62" s="3">
-        <v>137700</v>
+        <v>19100</v>
       </c>
       <c r="F62" s="3">
-        <v>138500</v>
+        <v>17100</v>
       </c>
       <c r="G62" s="3">
-        <v>104700</v>
+        <v>75800</v>
       </c>
       <c r="H62" s="3">
-        <v>109300</v>
+        <v>69900</v>
       </c>
       <c r="I62" s="3">
-        <v>110900</v>
+        <v>72000</v>
       </c>
       <c r="J62" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K62" s="3">
         <v>118400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>114400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>106500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>108600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>112100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>116400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>121400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>144200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>111800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>114700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>119900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>99700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>96700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>52700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>56800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>48700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>46600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>44200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>42300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>40800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>46000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>36900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>35900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>34300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>49300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5802,8 +5951,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5903,8 +6055,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6004,109 +6159,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1646400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1635600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1235600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1257100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1117600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1097600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1116800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1102100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1136100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1050100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1110300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1100600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1102900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1117100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1088300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>598900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>750300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>824600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>680000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>663200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>606800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>668600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>606900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>584500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>564400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>567100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>484900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>488900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>469900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>478600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>499100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>535500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>585700</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6142,8 +6303,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6243,8 +6405,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6344,8 +6509,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6445,8 +6613,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6546,109 +6717,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>368500</v>
+      </c>
+      <c r="E72" s="3">
         <v>386600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>360500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>340100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>308900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>284000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>253200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>223800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>204400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>222300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>202400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>192700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>169400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>154600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>158000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>169000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>137100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>89000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>78500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>69900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>85600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>99400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>161400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>140600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>194400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>189900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>266900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>323600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>330200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>310100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>289900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>341100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>325700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6748,8 +6925,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6849,8 +7029,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6950,109 +7133,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>878900</v>
+      </c>
+      <c r="E76" s="3">
         <v>905400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>960000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>943300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>893700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>864600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>818000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>776000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>729000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>770400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>749400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>730800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>698500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>677100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>731700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>719200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>667900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>608600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>587100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>574600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>583800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>591000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>667900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>643100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>701300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>674100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>752400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>822800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>801300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>772800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>739600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>770900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7152,215 +7341,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44562</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44191</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E81" s="3">
         <v>38400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>31200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>41000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>29400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>32900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>33200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>23200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>48100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>17600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>29900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>37500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>20800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>18700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>11900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>20100</v>
       </c>
       <c r="AF81" s="3">
         <v>20100</v>
       </c>
       <c r="AG81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-51100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>15400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7396,109 +7594,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>29100</v>
+        <v>11400</v>
       </c>
       <c r="E83" s="3">
-        <v>27600</v>
+        <v>15400</v>
       </c>
       <c r="F83" s="3">
+        <v>13500</v>
+      </c>
+      <c r="G83" s="3">
+        <v>13200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="I83" s="3">
+        <v>13700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K83" s="3">
+        <v>23600</v>
+      </c>
+      <c r="L83" s="3">
+        <v>23400</v>
+      </c>
+      <c r="M83" s="3">
+        <v>22400</v>
+      </c>
+      <c r="N83" s="3">
+        <v>24800</v>
+      </c>
+      <c r="O83" s="3">
+        <v>24400</v>
+      </c>
+      <c r="P83" s="3">
         <v>23500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="Q83" s="3">
+        <v>25000</v>
+      </c>
+      <c r="R83" s="3">
+        <v>21900</v>
+      </c>
+      <c r="S83" s="3">
+        <v>20800</v>
+      </c>
+      <c r="T83" s="3">
+        <v>20900</v>
+      </c>
+      <c r="U83" s="3">
+        <v>20700</v>
+      </c>
+      <c r="V83" s="3">
+        <v>28800</v>
+      </c>
+      <c r="W83" s="3">
+        <v>27100</v>
+      </c>
+      <c r="X83" s="3">
+        <v>27000</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>27400</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>29800</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>27900</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>25300</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>26400</v>
+      </c>
+      <c r="AD83" s="3">
         <v>23000</v>
       </c>
-      <c r="H83" s="3">
-        <v>23000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>23900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>23600</v>
-      </c>
-      <c r="K83" s="3">
-        <v>23400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>22400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>24800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>24400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>23500</v>
-      </c>
-      <c r="P83" s="3">
-        <v>25000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>21900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>20800</v>
-      </c>
-      <c r="S83" s="3">
-        <v>20900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>20700</v>
-      </c>
-      <c r="U83" s="3">
-        <v>28800</v>
-      </c>
-      <c r="V83" s="3">
-        <v>27100</v>
-      </c>
-      <c r="W83" s="3">
-        <v>27000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>27400</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>29800</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>27900</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>25300</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>26400</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>23000</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>22300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>22200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>21800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>22200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>22300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7598,8 +7800,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7699,8 +7904,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7800,8 +8008,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7901,8 +8112,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8002,109 +8216,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>64100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>99100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>79600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>64400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>87000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>42000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>68100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>62400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>43500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>66300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>29200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>11800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>46400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>79300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>29900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>20600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>58200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>57400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>23100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>57600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>65400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>58900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>38400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>34600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>55200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8140,109 +8360,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-22300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-24700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-45500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-35100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-20400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-48500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8342,8 +8566,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8443,109 +8670,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-139200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-268900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-36500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-58200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-34500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-429100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>37100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-45100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>6000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-27600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-26300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-14600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8581,31 +8814,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8682,8 +8916,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8783,8 +9020,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8884,8 +9124,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8985,307 +9228,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-74800</v>
+      </c>
+      <c r="E100" s="3">
         <v>333700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-63500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>109400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-49700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-25700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-23400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>432800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-149900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-64300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>149000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>11400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-46200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-112500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>16100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>7000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-76200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>18700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>8300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-12700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-10400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="E101" s="3">
-        <v>-2700</v>
+        <v>-2000</v>
       </c>
       <c r="F101" s="3">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="G101" s="3">
-        <v>-1500</v>
+        <v>4600</v>
       </c>
       <c r="H101" s="3">
-        <v>-2000</v>
+        <v>-4000</v>
       </c>
       <c r="I101" s="3">
-        <v>500</v>
+        <v>-4900</v>
       </c>
       <c r="J101" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K101" s="3">
         <v>4600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>1500</v>
       </c>
       <c r="T101" s="3">
         <v>1500</v>
       </c>
       <c r="U101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V101" s="3">
         <v>-1700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E102" s="3">
         <v>165600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-157000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>65300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>60500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>26300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-44500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>22600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>44500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-90200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>138400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>10900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-78200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>20900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>7700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>48000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>31900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>32200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>9900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>20600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>HAE</t>
   </si>
@@ -656,462 +656,474 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44562</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44191</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43099</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>348500</v>
+      </c>
+      <c r="E8" s="3">
         <v>345500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>336200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>343300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>336300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>318200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>311300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>304400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>305300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>297500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>261500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>265000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>259800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>239900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>228500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>225000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>240400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>209500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>195600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>238500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>259000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>252600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>238500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>249300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>247400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>241600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>229300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>233600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>234000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>225400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>211000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>228100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>227800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>148600</v>
+      </c>
+      <c r="E9" s="3">
         <v>154300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>151600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>154300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>151300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>147600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>143900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>140200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>146600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>139600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>119400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>128700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>121400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>117100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>118200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>143100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>120200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>104000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>105000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>124900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>130900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>125600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>122500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>138100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>136200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>129700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>124900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>129200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>122700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>120800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>119300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>146000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>126800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>199900</v>
+      </c>
+      <c r="E10" s="3">
         <v>191200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>184500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>188900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>184900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>170600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>167500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>164300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>158700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>157900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>142100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>136300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>138400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>122800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>110300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>82000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>120200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>105500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>90600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>113600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>128100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>127000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>116000</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>111200</v>
       </c>
       <c r="AA10" s="3">
         <v>111200</v>
       </c>
       <c r="AB10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="AC10" s="3">
         <v>111900</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>104400</v>
       </c>
       <c r="AD10" s="3">
         <v>104400</v>
       </c>
       <c r="AE10" s="3">
+        <v>104400</v>
+      </c>
+      <c r="AF10" s="3">
         <v>111300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>104600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>91700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>82100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>101000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1148,112 +1160,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E12" s="3">
         <v>16500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>12900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12700</v>
-      </c>
-      <c r="L12" s="3">
-        <v>10900</v>
       </c>
       <c r="M12" s="3">
         <v>10900</v>
       </c>
       <c r="N12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="O12" s="3">
         <v>13200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>11100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>12400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>9300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1356,162 +1372,168 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E14" s="3">
         <v>6000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>26300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>23500</v>
       </c>
-      <c r="G14" s="3">
-        <v>8000</v>
-      </c>
       <c r="H14" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I14" s="3">
         <v>7300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>11000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>16600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-1200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-31600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>10300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>51700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>6400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>24500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>31700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>57200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>400</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E15" s="3">
         <v>12300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>32800</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>10</v>
@@ -1525,8 +1547,8 @@
       <c r="W15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1564,8 +1586,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1599,216 +1624,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>282400</v>
+      </c>
+      <c r="E17" s="3">
         <v>287800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>270100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>289900</v>
       </c>
-      <c r="G17" s="3">
-        <v>282300</v>
-      </c>
       <c r="H17" s="3">
+        <v>277300</v>
+      </c>
+      <c r="I17" s="3">
         <v>275600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>257700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>258200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>262000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>250800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>230700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>245800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>224100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>215400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>227100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>246200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>199900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>150700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>183900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>212500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>218100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>202800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>251800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>225400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>219000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>215500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>224100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>219300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>233000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>201100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>186300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>285600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>206600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E18" s="3">
         <v>57700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>66000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>53400</v>
       </c>
-      <c r="G18" s="3">
-        <v>53900</v>
-      </c>
       <c r="H18" s="3">
+        <v>59000</v>
+      </c>
+      <c r="I18" s="3">
         <v>42600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>53600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>46300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>43300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>30800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>35700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>24500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>40500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>58800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>26000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>40900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>49800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-13300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>23900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>28400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>26100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>24300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>24700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-57500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>21200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1845,242 +1877,249 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3">
         <v>-7000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5100</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="3">
         <v>2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-6200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-3800</v>
       </c>
       <c r="U20" s="3">
         <v>-3800</v>
       </c>
       <c r="V20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="W20" s="3">
         <v>-4100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-1400</v>
       </c>
       <c r="AG20" s="3">
         <v>-1400</v>
       </c>
       <c r="AH20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E21" s="3">
         <v>70000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>85500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>69000</v>
       </c>
-      <c r="G21" s="3">
-        <v>60900</v>
-      </c>
       <c r="H21" s="3">
+        <v>65900</v>
+      </c>
+      <c r="I21" s="3">
         <v>49800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>59100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>52600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>65800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>64500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>47900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>40100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>55800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>43500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>25000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>58100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>75800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>28700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>50700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>64900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>72100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>51600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>53400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>48300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>29700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>36300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>22500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>45100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>45000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>41200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E22" s="3">
         <v>7000</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2500</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1000</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>10</v>
@@ -2097,11 +2136,11 @@
       <c r="P22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R22" s="3">
         <v>3000</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>10</v>
@@ -2118,8 +2157,8 @@
       <c r="W22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -2157,216 +2196,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E23" s="3">
         <v>44700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>46700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>44000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>32800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>51600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>42200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>31400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>19900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-27400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>37400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>55000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>22000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>37800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>45100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-17700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>21800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>25500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>23000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>13300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>22900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>23300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-59200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E24" s="3">
         <v>10900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7900</v>
-      </c>
-      <c r="M24" s="3">
-        <v>5600</v>
       </c>
       <c r="N24" s="3">
         <v>5600</v>
       </c>
       <c r="O24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="P24" s="3">
         <v>8200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-16400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-21300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2469,216 +2517,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E26" s="3">
         <v>33800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>38400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>31200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>41000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>32900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>33200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>23200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-11000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>48100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>17600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>29900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>37500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>20800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>18300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>18700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>11600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>21600</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>20100</v>
       </c>
       <c r="AG26" s="3">
         <v>20100</v>
       </c>
       <c r="AH26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-51100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E27" s="3">
         <v>33800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>38400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>31200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>41000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>32900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>33200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>23200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-11000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>48100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>17600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>29900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>37500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>20800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>18300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>18700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>11600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>21600</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>20100</v>
       </c>
       <c r="AG27" s="3">
         <v>20100</v>
       </c>
       <c r="AH27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-51100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2781,8 +2838,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2846,8 +2906,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>10</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>10</v>
@@ -2864,14 +2924,14 @@
       <c r="AC29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE29" s="3">
         <v>300</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-28100</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>10</v>
@@ -2885,8 +2945,11 @@
       <c r="AJ29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2989,8 +3052,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3093,216 +3159,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3">
         <v>7000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5100</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="3">
         <v>-2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>6200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>3800</v>
       </c>
       <c r="U32" s="3">
         <v>3800</v>
       </c>
       <c r="V32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W32" s="3">
         <v>4100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>800</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>1400</v>
       </c>
       <c r="AG32" s="3">
         <v>1400</v>
       </c>
       <c r="AH32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AI32" s="3">
         <v>1700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E33" s="3">
         <v>33800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>38400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>31200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>41000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>32900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>33200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>23200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>48100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>17600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>29900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>37500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>20800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>18300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>18700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>11900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>20100</v>
       </c>
       <c r="AG33" s="3">
         <v>20100</v>
       </c>
       <c r="AH33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-51100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3405,221 +3480,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E35" s="3">
         <v>33800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>38400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>31200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>41000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>32900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>33200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>23200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>48100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>17600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>29900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>37500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>20800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>18300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>18700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>11900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>20100</v>
       </c>
       <c r="AG35" s="3">
         <v>20100</v>
       </c>
       <c r="AH35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-51100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44562</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44191</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43099</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3656,8 +3740,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3694,139 +3779,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>320800</v>
+      </c>
+      <c r="E41" s="3">
         <v>299300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>344400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>178800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>194000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>351000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>285700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>284500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>224000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>241200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>214900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>259500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>236900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>192400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>173500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>192300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>189000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>279200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>275700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>137300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>126400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>112000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>190200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>169400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>154900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>199800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>192100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>180200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>251600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>203600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>171700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>139600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>129600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>138900</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3902,450 +3991,465 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>211900</v>
+      </c>
+      <c r="E43" s="3">
         <v>213500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>201500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>206600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>211600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>174200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>177100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>179100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>181100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>171500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>146500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>159400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>155000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>141300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>132900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>127600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>146900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>141500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>141100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>165200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>170800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>176500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>163300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>185000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>167600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>161600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>151300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>151200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>146700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>143700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>151500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>152700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>150600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>359600</v>
+      </c>
+      <c r="E44" s="3">
         <v>382100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>373800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>317200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>304000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>285800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>289200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>259400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>255800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>254700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>277900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>293000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>305700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>322700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>326500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>322600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>299700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>305200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>294500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>270300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>254200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>244500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>222000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>194300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>168900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>163600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>175300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>160800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>158800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>168600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>173900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>176900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>188500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>1900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>45500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>48400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>48500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>44100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>51500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>51100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>32700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>34400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>48100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>30800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>31200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>34700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>39800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>27400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>24400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>27900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>32200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>29000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>32600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>37500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>30900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>40900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1005900</v>
+      </c>
+      <c r="E46" s="3">
         <v>955900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>978600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>768900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>765000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>865700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>801600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>769700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>706300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>715800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>687800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>756000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>729500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>699200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>684400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>693500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>668300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>760300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>759400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>603600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>582600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>567800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>615300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>576100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>515900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>552800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>551000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>521200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>589700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>553400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>528100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>510000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>496600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>512400</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>500</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4422,216 +4526,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>286100</v>
+      </c>
+      <c r="E48" s="3">
         <v>300500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>302500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>366600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>318700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>307800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>304500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>364300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>313100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>307800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>288300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>258500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>238800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>223700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>214800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>217600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>240000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>240400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>243000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>305600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>322300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>264200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>276700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>344000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>351100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>344600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>315900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>332200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>330000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>320200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>322000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>323900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>336000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1070900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1104000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1108300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>971200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>984300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>715900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>734100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>742000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>750500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>757600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>768800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>777500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>792200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>805800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>820000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>831900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>335200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>341800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>354800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>343800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>318400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>324600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>331500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>338500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>345400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>352300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>359600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>368000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>375000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>380500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>384400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>388400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>452700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4734,8 +4847,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4838,112 +4954,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>156300</v>
+      </c>
+      <c r="E52" s="3">
         <v>155800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>134700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>81100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>127400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>116600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>117300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>53600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>108100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>83900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>75600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>67700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>70900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>72700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>75000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>76900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>74500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>75700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>76000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>14100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>33900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>36100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>16200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>15200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>16000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>14600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>16900</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>17000</v>
       </c>
       <c r="AG52" s="3">
         <v>17000</v>
       </c>
       <c r="AH52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AI52" s="3">
         <v>16400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>21200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5046,112 +5168,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2531300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2525200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2541000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2195600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2200400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2011300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1962300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1934800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1878100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1865100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1820500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1859700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1831400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1801500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1794200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1819900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1318100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1418200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1433200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1267100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1237700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1190500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1259600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1274800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1227600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1265700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1241200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1237300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1311700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1271200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1251400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1238700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1306400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1334800</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5188,8 +5316,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5226,632 +5355,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E57" s="3">
         <v>69200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>76900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>73400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>56800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>80200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>78100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>63900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>63800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>61500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>57900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>58400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>51200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>49100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>50300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>43000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>49100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>48500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>50700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>52300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>57400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>60800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>63400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>62600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>57900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>65400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>55300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>41500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>41800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>39400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>43000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>48800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E58" s="3">
         <v>5400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>13600</v>
       </c>
       <c r="I58" s="3">
         <v>13600</v>
       </c>
       <c r="J58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="K58" s="3">
         <v>18900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>58200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>214100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>144100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>82700</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>17000</v>
       </c>
       <c r="R58" s="3">
         <v>17000</v>
       </c>
       <c r="S58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="T58" s="3">
         <v>17100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>167000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>231400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>77000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>62000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>56900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>117500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>27700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>17200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>12700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>17000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>194300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>151500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>108600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>65900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>61000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>66300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>139200</v>
+      </c>
+      <c r="E59" s="3">
         <v>150000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>137300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>128000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>132400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>124900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>112300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>104500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>153200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>142500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>115700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>169700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>160200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>160800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>162200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>186200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>134400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>122500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>128000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>147100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>142400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>125700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>115300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>144700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>131500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>118600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>111600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>135200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>131200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>104600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>100300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>107200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>101100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>253200</v>
+      </c>
+      <c r="E60" s="3">
         <v>273900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>260100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>300400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>261800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>264200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>236900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>251800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>226900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>262200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>180500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>442300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>355400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>288500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>228300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>253500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>194400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>338600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>407800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>274800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>256700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>240100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>293700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>235800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>211300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>189200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>194000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>384700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>324200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>255000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>205500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>211200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>216200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1288300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1309500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1291600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>855500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>857300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>748700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>751400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>811800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>756800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>759600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>763100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>559400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>633100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>698000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>767300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>690600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>292700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>297000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>296900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>305500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>309700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>314000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>318100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>322500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>326600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>331000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>330800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>59400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>118700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>178000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>237200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>253600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>270000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>75800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>69900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>72000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>118400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>114400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>106500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>108600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>112100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>116400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>121400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>144200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>111800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>114700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>119900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>99700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>96700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>52700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>56800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>48700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>46600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>44200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>42300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>40800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>46000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>36900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>35900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>34300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>49300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5954,8 +6102,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6058,8 +6209,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6162,112 +6316,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1624400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1646400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1635600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1235600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1257100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1117600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1097600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1116800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1102100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1136100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1050100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1110300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1100600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1102900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1117100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1088300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>598900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>750300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>824600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>680000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>663200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>606800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>668600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>606900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>584500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>564400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>567100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>484900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>488900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>469900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>478600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>499100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>535500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>585700</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6304,8 +6464,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6408,8 +6569,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6512,8 +6676,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6616,8 +6783,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6720,112 +6890,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>392200</v>
+      </c>
+      <c r="E72" s="3">
         <v>368500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>386600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>360500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>340100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>308900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>284000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>253200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>223800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>204400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>222300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>202400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>192700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>169400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>154600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>158000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>169000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>137100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>89000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>78500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>69900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>85600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>99400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>161400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>140600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>194400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>189900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>266900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>323600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>330200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>310100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>289900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>341100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>325700</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6928,8 +7104,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7032,8 +7211,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7136,112 +7318,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>906900</v>
+      </c>
+      <c r="E76" s="3">
         <v>878900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>905400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>960000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>943300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>893700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>864600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>818000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>776000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>729000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>770400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>749400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>730800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>698500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>677100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>731700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>719200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>667900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>608600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>587100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>574600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>583800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>591000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>667900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>643100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>701300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>674100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>752400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>822800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>801300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>772800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>739600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>770900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7344,221 +7532,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44562</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44191</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43099</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E81" s="3">
         <v>33800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>38400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>31200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>41000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>32900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>33200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>23200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>48100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>17600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>29900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>37500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>20800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>18300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>18700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>11900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>20100</v>
       </c>
       <c r="AG81" s="3">
         <v>20100</v>
       </c>
       <c r="AH81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-51100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7595,112 +7792,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E83" s="3">
         <v>11400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>22400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>21900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>20900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>28800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>27100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>27000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>27400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>29800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>27900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>25300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>26400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>23000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>22300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>22200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>22300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7803,8 +8004,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7907,8 +8111,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8011,8 +8218,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8115,8 +8325,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8219,112 +8432,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E89" s="3">
         <v>48800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-27400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>64100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>99100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>79600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>64400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>87000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>42000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>68100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>62400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>43500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>66300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>29200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>46400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>79300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>29900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>20600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>58200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>57400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>23100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>57600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>65400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>58900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>38400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>34600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8361,112 +8580,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-22300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-24700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-36000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-45500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-35100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-20400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-48500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8569,8 +8792,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8673,112 +8899,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-139200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-268900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-25100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-58200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-34500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-429100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>37100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-23900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-45100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>6000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-13200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-27600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-26300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-14600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8815,8 +9047,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8841,8 +9074,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8919,8 +9152,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9023,8 +9259,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9127,8 +9366,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9231,316 +9473,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-74800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>333700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-63500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>109400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-49700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-25700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-23400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>432800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-149900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-64300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>149000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>11400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-46200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-112500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>16100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>7000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-76200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>18700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>8300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-12700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-10400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3100</v>
-      </c>
-      <c r="T101" s="3">
-        <v>1500</v>
       </c>
       <c r="U101" s="3">
         <v>1500</v>
       </c>
       <c r="V101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W101" s="3">
         <v>-1700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-45100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>165600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-157000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>65300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>60500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>26300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-44500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>22600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>44500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-18800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-90200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>138400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>14400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-78200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>20900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>7700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>11900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>48000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>31900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>32200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>9900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>20600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>HAE</t>
   </si>
@@ -656,474 +656,487 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44562</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44191</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43099</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>330600</v>
+      </c>
+      <c r="E8" s="3">
         <v>348500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>345500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>336200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>343300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>336300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>318200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>311300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>304400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>305300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>297500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>261500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>265000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>259800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>239900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>228500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>225000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>240400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>209500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>195600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>238500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>259000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>252600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>238500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>249300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>247400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>241600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>229300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>233600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>234000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>225400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>211000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>228100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>227800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E9" s="3">
         <v>148600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>154300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>151600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>154300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>151300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>147600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>143900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>140200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>146600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>139600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>119400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>128700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>121400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>117100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>118200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>143100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>120200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>104000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>105000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>124900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>130900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>125600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>122500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>138100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>136200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>129700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>124900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>129200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>122700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>120800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>119300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>146000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>126800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>199100</v>
+      </c>
+      <c r="E10" s="3">
         <v>199900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>191200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>184500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>188900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>184900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>170600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>167500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>164300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>158700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>157900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>142100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>136300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>138400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>122800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>110300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>82000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>120200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>105500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>90600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>113600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>128100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>127000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>116000</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>111200</v>
       </c>
       <c r="AB10" s="3">
         <v>111200</v>
       </c>
       <c r="AC10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="AD10" s="3">
         <v>111900</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>104400</v>
       </c>
       <c r="AE10" s="3">
         <v>104400</v>
       </c>
       <c r="AF10" s="3">
+        <v>104400</v>
+      </c>
+      <c r="AG10" s="3">
         <v>111300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>104600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>91700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>82100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>101000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1161,115 +1174,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E12" s="3">
         <v>15800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>12900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12700</v>
-      </c>
-      <c r="M12" s="3">
-        <v>10900</v>
       </c>
       <c r="N12" s="3">
         <v>10900</v>
       </c>
       <c r="O12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="P12" s="3">
         <v>13200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>8600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>11100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>12400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>8200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>8500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1375,168 +1392,174 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E14" s="3">
         <v>7100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>26300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>23500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>13000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7300</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>11000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>16600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-1200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-31600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>51700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>24500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>31700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>57200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>400</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E15" s="3">
         <v>12200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>11400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>12400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>32800</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>10</v>
@@ -1550,8 +1573,8 @@
       <c r="X15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1589,8 +1612,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1625,222 +1651,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>274100</v>
+      </c>
+      <c r="E17" s="3">
         <v>282400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>287800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>270100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>289900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>277300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>275600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>257700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>258200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>262000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>250800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>230700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>245800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>224100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>215400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>227100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>246200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>199900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>150700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>183900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>212500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>218100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>202800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>251800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>225400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>219000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>215500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>224100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>219300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>233000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>201100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>186300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>285600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>206600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E18" s="3">
         <v>66100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>57700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>66000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>53400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>59000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>42600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>53600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>46300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>43300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>46700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>30800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>35700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>24500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-21200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>40500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>58800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>26000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>40900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>49800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-13300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>23900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>28400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>26100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>24300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>24700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-57500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>21200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1878,8 +1911,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1889,240 +1923,246 @@
       <c r="E20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3">
         <v>-7000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5100</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-3800</v>
       </c>
       <c r="V20" s="3">
         <v>-3800</v>
       </c>
       <c r="W20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="X20" s="3">
         <v>-4100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-1400</v>
       </c>
       <c r="AH20" s="3">
         <v>-1400</v>
       </c>
       <c r="AI20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E21" s="3">
         <v>78300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>70000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>85500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>69000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>65900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>49800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>59100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>52600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>65800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>64500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>47900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>40100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>55800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>43500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>25000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>58100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>75800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>50700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>64900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>72100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>51600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>53400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>48300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>29700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>36300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>22500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>45100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>45000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>41200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E22" s="3">
         <v>9100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7000</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2500</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>10</v>
@@ -2139,11 +2179,11 @@
       <c r="Q22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S22" s="3">
         <v>3000</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>10</v>
@@ -2160,8 +2200,8 @@
       <c r="X22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2199,222 +2239,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E23" s="3">
         <v>49900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>44700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>46700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>44000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>51600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>32600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>42200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>41100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>25500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>15300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>31400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>19900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-27400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>37400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>55000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>22000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>37800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>45100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-17700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>25500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>23000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>13300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>22900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>23300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-59200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>18900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E24" s="3">
         <v>12400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7900</v>
-      </c>
-      <c r="N24" s="3">
-        <v>5600</v>
       </c>
       <c r="O24" s="3">
         <v>5600</v>
       </c>
       <c r="P24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Q24" s="3">
         <v>8200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-16400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-21300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2520,222 +2569,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E26" s="3">
         <v>37500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>33800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>38400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>20400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>31200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>41000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>29400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>32900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>33200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>23200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>48100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>17600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>29900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>37500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>20800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>18300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>18700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>11600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21600</v>
-      </c>
-      <c r="AG26" s="3">
-        <v>20100</v>
       </c>
       <c r="AH26" s="3">
         <v>20100</v>
       </c>
       <c r="AI26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-51100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>15400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E27" s="3">
         <v>37500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>33800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>38400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>31200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>41000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>29400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>32900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>33200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>23200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>31900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>48100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>17600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>29900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>37500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>20800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>18300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>18700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>11600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>21600</v>
-      </c>
-      <c r="AG27" s="3">
-        <v>20100</v>
       </c>
       <c r="AH27" s="3">
         <v>20100</v>
       </c>
       <c r="AI27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-51100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>15400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2841,8 +2899,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2909,8 +2970,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>10</v>
@@ -2927,14 +2988,14 @@
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF29" s="3">
         <v>300</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-28100</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>10</v>
@@ -2948,8 +3009,11 @@
       <c r="AK29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3055,8 +3119,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3162,8 +3229,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3173,211 +3243,217 @@
       <c r="E32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3">
         <v>7000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5100</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>3800</v>
       </c>
       <c r="V32" s="3">
         <v>3800</v>
       </c>
       <c r="W32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X32" s="3">
         <v>4100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>800</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>1400</v>
       </c>
       <c r="AH32" s="3">
         <v>1400</v>
       </c>
       <c r="AI32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E33" s="3">
         <v>37500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>33800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>38400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>20400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>31200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>41000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>29400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>32900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>33200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>23200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>31900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>48100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>17600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>29900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>37500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>20800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>18300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>18700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>11900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>20100</v>
       </c>
       <c r="AH33" s="3">
         <v>20100</v>
       </c>
       <c r="AI33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-51100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>15400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3483,227 +3559,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E35" s="3">
         <v>37500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>33800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>38400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>20400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>31200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>41000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>29400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>32900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>33200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>23200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>31900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>48100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>17600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>29900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>37500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>20800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>18300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>18700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>11900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>20100</v>
       </c>
       <c r="AH35" s="3">
         <v>20100</v>
       </c>
       <c r="AI35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-51100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>15400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44562</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44191</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43099</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3741,8 +3826,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3780,145 +3866,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>306800</v>
+      </c>
+      <c r="E41" s="3">
         <v>320800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>299300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>344400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>178800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>194000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>351000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>285700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>284500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>224000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>241200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>214900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>259500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>236900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>192400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>173500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>192300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>189000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>279200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>275700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>137300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>126400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>112000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>190200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>169400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>154900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>199800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>192100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>180200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>251600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>203600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>171700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>139600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>129600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>138900</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3994,465 +4084,480 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>202700</v>
+      </c>
+      <c r="E43" s="3">
         <v>211900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>213500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>201500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>206600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>211600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>174200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>177100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>179100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>181100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>171500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>146500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>159400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>155000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>141300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>132900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>127600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>146900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>141500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>141100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>165200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>170800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>176500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>163300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>185000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>167600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>161600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>151300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>151200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>146700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>143700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>151500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>152700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>150600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>365100</v>
+      </c>
+      <c r="E44" s="3">
         <v>359600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>382100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>373800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>317200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>304000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>285800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>289200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>259400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>255800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>254700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>277900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>293000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>305700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>322700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>326500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>322600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>299700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>305200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>294500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>270300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>254200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>244500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>222000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>194300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>168900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>163600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>175300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>160800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>158800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>168600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>173900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>176900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>188500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>1900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>48400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>48500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>44100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>42900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>51500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>51100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>32700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>34400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>48100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>30800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>31200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>34700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>39800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>27400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>24400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>27900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>32200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>29000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>32600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>37500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>30900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>40900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>27900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>935000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1005900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>955900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>978600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>768900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>765000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>865700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>801600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>769700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>706300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>715800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>687800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>756000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>729500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>699200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>684400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>693500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>668300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>760300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>759400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>603600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>582600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>567800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>615300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>576100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>515900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>552800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>551000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>521200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>589700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>553400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>528100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>510000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>496600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>512400</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3">
         <v>4100</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>100</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>500</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4529,222 +4634,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>284100</v>
+      </c>
+      <c r="E48" s="3">
         <v>286100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>300500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>302500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>366600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>318700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>307800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>304500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>364300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>313100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>307800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>288300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>258500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>238800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>223700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>214800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>217600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>240000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>240400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>243000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>305600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>322300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>264200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>276700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>344000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>351100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>344600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>315900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>332200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>330000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>320200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>322000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>323900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>336000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1060000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1070900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1104000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1108300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>971200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>984300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>715900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>734100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>742000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>750500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>757600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>768800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>777500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>792200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>805800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>820000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>831900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>335200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>341800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>354800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>343800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>318400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>324600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>331500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>338500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>345400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>352300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>359600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>368000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>375000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>380500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>384400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>388400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>452700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4850,8 +4964,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4957,115 +5074,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>171900</v>
+      </c>
+      <c r="E52" s="3">
         <v>156300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>155800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>134700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>81100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>127400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>116600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>117300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>53600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>108100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>83900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>75600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>67700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>70900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>72700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>75000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>76900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>74500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>75700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>76000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>14100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>33900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>36100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>16200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>15200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>16000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>14600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>16000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>16900</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>17000</v>
       </c>
       <c r="AH52" s="3">
         <v>17000</v>
       </c>
       <c r="AI52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>16400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>21200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5171,115 +5294,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2450900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2531300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2525200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2541000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2195600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2200400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2011300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1962300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1934800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1878100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1865100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1820500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1859700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1831400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1801500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1794200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1819900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1318100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1418200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1433200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1267100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1237700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1190500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1259600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1274800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1227600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1265700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1241200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1237300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1311700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1271200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1251400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1238700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1306400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1334800</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5317,8 +5446,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5356,650 +5486,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="3">
         <v>63000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>69200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>76900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>73400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>56800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>80200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>78100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>63900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>61500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>57900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>58400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>51200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>45000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>49100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>50300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>43000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>49100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>48500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>50700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>52300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>57400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>60800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>63400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>62600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>57900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>65400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>55300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>41500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>41800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>39400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>43000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>48800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>303600</v>
+      </c>
+      <c r="E58" s="3">
         <v>5100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>13600</v>
       </c>
       <c r="J58" s="3">
         <v>13600</v>
       </c>
       <c r="K58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="L58" s="3">
         <v>18900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>58200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>214100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>144100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>82700</v>
-      </c>
-      <c r="R58" s="3">
-        <v>17000</v>
       </c>
       <c r="S58" s="3">
         <v>17000</v>
       </c>
       <c r="T58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="U58" s="3">
         <v>17100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>167000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>231400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>77000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>62000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>56900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>117500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>27700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>17200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>12700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>17000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>194300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>151500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>108600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>65900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>61000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>66300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>274600</v>
+      </c>
+      <c r="E59" s="3">
         <v>139200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>150000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>137300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>128000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>132400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>124900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>112300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>104500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>153200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>142500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>115700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>169700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>160200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>160800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>162200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>186200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>134400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>122500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>128000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>147100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>142400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>125700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>115300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>144700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>131500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>118600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>111600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>135200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>131200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>104600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>100300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>107200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>101100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>578100</v>
+      </c>
+      <c r="E60" s="3">
         <v>253200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>273900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>260100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>300400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>261800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>264200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>236900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>251800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>226900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>262200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>180500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>442300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>355400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>288500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>228300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>253500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>194400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>338600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>407800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>274800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>256700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>240100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>293700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>235800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>211300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>189200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>194000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>384700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>324200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>255000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>205500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>211200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>216200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1052000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1288300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1309500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1291600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>855500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>857300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>748700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>751400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>811800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>756800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>759600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>763100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>559400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>633100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>698000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>767300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>690600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>292700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>297000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>296900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>305500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>309700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>314000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>318100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>322500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>326600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>331000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>330800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>59400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>118700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>178000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>237200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>253600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>270000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="3">
         <v>21400</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>75800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>69900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>72000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>118400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>114400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>106500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>108600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>112100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>116400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>121400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>144200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>111800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>114700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>119900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>99700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>96700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>52700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>56800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>48700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>46600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>44200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>42300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>40800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>46000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>36900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>35900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>34300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>49300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6105,8 +6254,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6212,8 +6364,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6319,115 +6474,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1630100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1624400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1646400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1635600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1235600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1257100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1117600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1097600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1116800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1102100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1136100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1050100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1110300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1100600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1102900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1117100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1088300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>598900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>750300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>824600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>680000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>663200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>606800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>668600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>606900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>584500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>564400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>567100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>484900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>488900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>469900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>478600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>499100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>535500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>585700</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6465,8 +6626,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6572,8 +6734,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6679,8 +6844,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6786,8 +6954,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6893,115 +7064,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="3">
         <v>392200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>368500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>386600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>360500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>340100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>308900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>284000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>253200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>223800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>204400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>222300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>202400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>192700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>169400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>154600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>158000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>169000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>137100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>89000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>78500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>69900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>85600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>99400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>161400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>140600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>194400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>189900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>266900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>323600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>330200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>310100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>289900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>341100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>325700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7107,8 +7284,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7214,8 +7394,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7321,115 +7504,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>820800</v>
+      </c>
+      <c r="E76" s="3">
         <v>906900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>878900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>905400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>960000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>943300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>893700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>864600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>818000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>776000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>729000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>770400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>749400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>730800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>698500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>677100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>731700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>719200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>667900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>608600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>587100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>574600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>583800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>591000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>667900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>643100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>701300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>674100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>752400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>822800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>801300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>772800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>739600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>770900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7535,227 +7724,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44562</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44191</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43099</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E81" s="3">
         <v>37500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>33800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>38400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>20400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>31200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>41000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>29400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>32900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>33200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>23200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>31900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>48100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>17600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>29900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>37500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>20800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>18300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>18700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>11900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>20100</v>
       </c>
       <c r="AH81" s="3">
         <v>20100</v>
       </c>
       <c r="AI81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-51100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>15400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7793,115 +7991,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E83" s="3">
         <v>14200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>11400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>22400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>23500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>21900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>20800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>28800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>27100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>27000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>27400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>29800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>27900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>25300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>26400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>23000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>22200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>21800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>22200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>22300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8007,8 +8209,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8114,8 +8319,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8221,8 +8429,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8328,8 +8539,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8435,115 +8649,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E89" s="3">
         <v>43800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>48800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>64100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>99100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>79600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>64400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>87000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>42000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>62400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>43500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>66300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>29200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>11800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>46400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>79300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>29900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>20600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>58200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>57400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>23100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>57600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>65400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>58900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>38400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>34600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>55200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8581,115 +8801,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-45500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-35100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-20400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-48500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8795,8 +9019,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8902,115 +9129,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-139200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-268900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-18000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-36500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-31100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-58200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-34500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-20500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-429100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>37100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-45100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>6000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-27600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-26300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-14600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9048,8 +9281,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9077,8 +9311,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9155,8 +9389,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9262,8 +9499,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9369,8 +9609,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9476,325 +9719,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-151500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-74800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>333700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-63500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>109400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-49700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-25700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-23400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>432800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-149900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-64300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>149000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>11400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-46200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-112500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>16100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>7000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-76200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>18700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>8300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-12700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-10400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3100</v>
-      </c>
-      <c r="U101" s="3">
-        <v>1500</v>
       </c>
       <c r="V101" s="3">
         <v>1500</v>
       </c>
       <c r="W101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X101" s="3">
         <v>-1700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E102" s="3">
         <v>21600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-45100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>165600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-157000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>65300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>60500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-44500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>22600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>44500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>19000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-90200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>138400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-78200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>20900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>14500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>7700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>11900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>48000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>31900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>32200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>20600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>HAE</t>
   </si>
@@ -656,487 +656,500 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44562</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44191</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43099</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>321400</v>
+      </c>
+      <c r="E8" s="3">
         <v>330600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>348500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>345500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>336200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>343300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>336300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>318200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>311300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>304400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>305300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>297500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>261500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>265000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>259800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>239900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>228500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>225000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>240400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>209500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>195600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>238500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>259000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>252600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>238500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>249300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>247400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>241600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>229300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>233600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>234000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>225400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>211000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>228100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>227800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>131500</v>
+        <v>129500</v>
       </c>
       <c r="E9" s="3">
+        <v>131400</v>
+      </c>
+      <c r="F9" s="3">
         <v>148600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>154300</v>
       </c>
-      <c r="G9" s="3">
-        <v>151600</v>
-      </c>
       <c r="H9" s="3">
+        <v>156900</v>
+      </c>
+      <c r="I9" s="3">
         <v>154300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>151300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>147600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>143900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>140200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>146600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>139600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>119400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>128700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>121400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>117100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>118200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>143100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>120200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>104000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>105000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>124900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>130900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>125600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>122500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>138100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>136200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>129700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>124900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>129200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>122700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>120800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>119300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>146000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>126800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>199100</v>
+        <v>191900</v>
       </c>
       <c r="E10" s="3">
+        <v>199200</v>
+      </c>
+      <c r="F10" s="3">
         <v>199900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>191200</v>
       </c>
-      <c r="G10" s="3">
-        <v>184500</v>
-      </c>
       <c r="H10" s="3">
+        <v>179300</v>
+      </c>
+      <c r="I10" s="3">
         <v>188900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>184900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>170600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>167500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>164300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>158700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>157900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>142100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>136300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>138400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>122800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>110300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>82000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>120200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>105500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>90600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>113600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>128100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>127000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>116000</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>111200</v>
       </c>
       <c r="AC10" s="3">
         <v>111200</v>
       </c>
       <c r="AD10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="AE10" s="3">
         <v>111900</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>104400</v>
       </c>
       <c r="AF10" s="3">
         <v>104400</v>
       </c>
       <c r="AG10" s="3">
+        <v>104400</v>
+      </c>
+      <c r="AH10" s="3">
         <v>111300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>104600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>91700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>82100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>101000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1175,118 +1188,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>15900</v>
+        <v>15600</v>
       </c>
       <c r="E12" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F12" s="3">
         <v>15800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16500</v>
       </c>
-      <c r="G12" s="3">
-        <v>14400</v>
-      </c>
       <c r="H12" s="3">
+        <v>14500</v>
+      </c>
+      <c r="I12" s="3">
         <v>14000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>12900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12700</v>
-      </c>
-      <c r="N12" s="3">
-        <v>10900</v>
       </c>
       <c r="O12" s="3">
         <v>10900</v>
       </c>
       <c r="P12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Q12" s="3">
         <v>13200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>8600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>11100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>12400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>9300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>8500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1395,174 +1412,180 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-17400</v>
+        <v>11100</v>
       </c>
       <c r="E14" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="F14" s="3">
         <v>7100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6000</v>
       </c>
-      <c r="G14" s="3">
-        <v>26300</v>
-      </c>
       <c r="H14" s="3">
-        <v>23500</v>
+        <v>11200</v>
       </c>
       <c r="I14" s="3">
+        <v>19500</v>
+      </c>
+      <c r="J14" s="3">
         <v>13000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>11000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>16600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-31600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>51700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>6400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>24500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>31700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>57200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>400</v>
       </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E15" s="3">
         <v>11300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>11400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>32800</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>10</v>
@@ -1576,8 +1599,8 @@
       <c r="Y15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1615,8 +1638,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1652,228 +1678,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>274100</v>
+        <v>256500</v>
       </c>
       <c r="E17" s="3">
+        <v>273700</v>
+      </c>
+      <c r="F17" s="3">
         <v>282400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>287800</v>
       </c>
-      <c r="G17" s="3">
-        <v>270100</v>
-      </c>
       <c r="H17" s="3">
-        <v>289900</v>
+        <v>285200</v>
       </c>
       <c r="I17" s="3">
+        <v>293900</v>
+      </c>
+      <c r="J17" s="3">
         <v>277300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>275600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>257700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>258200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>262000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>250800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>230700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>245800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>224100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>215400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>227100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>246200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>199900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>150700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>183900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>212500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>218100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>202800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>251800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>225400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>219000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>215500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>224100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>219300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>233000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>201100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>186300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>285600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>206600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>56500</v>
+        <v>64900</v>
       </c>
       <c r="E18" s="3">
+        <v>56900</v>
+      </c>
+      <c r="F18" s="3">
         <v>66100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57700</v>
       </c>
-      <c r="G18" s="3">
-        <v>66000</v>
-      </c>
       <c r="H18" s="3">
-        <v>53400</v>
+        <v>51000</v>
       </c>
       <c r="I18" s="3">
+        <v>49400</v>
+      </c>
+      <c r="J18" s="3">
         <v>59000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>42600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>53600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>46300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>43300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>30800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>35700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-21200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>40500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>58800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>26000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>40900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>49800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-13300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>23900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>28400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>26100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>14300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>24300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>24700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-57500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>21200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1912,260 +1945,267 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>10</v>
+      <c r="D20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-10500</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3">
         <v>-7000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>10</v>
+      <c r="I20" s="3">
+        <v>-6500</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3">
         <v>2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-3800</v>
       </c>
       <c r="W20" s="3">
         <v>-3800</v>
       </c>
       <c r="X20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-1400</v>
       </c>
       <c r="AI20" s="3">
         <v>-1400</v>
       </c>
       <c r="AJ20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>67800</v>
+        <v>71700</v>
       </c>
       <c r="E21" s="3">
+        <v>78700</v>
+      </c>
+      <c r="F21" s="3">
         <v>78300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>70000</v>
       </c>
-      <c r="G21" s="3">
-        <v>85500</v>
-      </c>
       <c r="H21" s="3">
-        <v>69000</v>
+        <v>70400</v>
       </c>
       <c r="I21" s="3">
+        <v>66300</v>
+      </c>
+      <c r="J21" s="3">
         <v>65900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>49800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>59100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>52600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>65800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>64500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>47900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>40100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>55800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>43500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>25000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>58100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>75800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>28700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>50700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>64900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>72100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>51600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>53400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>48300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>29700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>36300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>22500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>45100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>45000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>41200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3200</v>
+        <v>4100</v>
       </c>
       <c r="E22" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F22" s="3">
         <v>9100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7000</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="3">
-        <v>11600</v>
-      </c>
       <c r="I22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J22" s="3">
         <v>1900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2500</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1000</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>10</v>
@@ -2182,11 +2222,11 @@
       <c r="R22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T22" s="3">
         <v>3000</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>10</v>
@@ -2203,8 +2243,8 @@
       <c r="Y22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -2242,228 +2282,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E23" s="3">
         <v>70700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>49900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>44700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>46700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>44000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>51600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>32600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>42200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>25500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>31400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-27400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>37400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>55000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>8000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>22000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>37800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>45100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-17700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>25500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>23000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>13300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>22900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-59200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>18900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E24" s="3">
         <v>12800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7900</v>
-      </c>
-      <c r="O24" s="3">
-        <v>5600</v>
       </c>
       <c r="P24" s="3">
         <v>5600</v>
       </c>
       <c r="Q24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="R24" s="3">
         <v>8200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-16400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-21300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2572,228 +2621,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E26" s="3">
         <v>58000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>37500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>33800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>38400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>20400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>31200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>41000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>29400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>32900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>33200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>23200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>14900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>48100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>17600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>29900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>37500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>20800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>18300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>18700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>11600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>21600</v>
-      </c>
-      <c r="AH26" s="3">
-        <v>20100</v>
       </c>
       <c r="AI26" s="3">
         <v>20100</v>
       </c>
       <c r="AJ26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-51100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>15400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E27" s="3">
         <v>58000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>37500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>33800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>38400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>20400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>31200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>41000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>29400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>32900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>33200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>23200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>14900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>31900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>48100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>17600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>29900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>37500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>20800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>18300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>18700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>11600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>21600</v>
-      </c>
-      <c r="AH27" s="3">
-        <v>20100</v>
       </c>
       <c r="AI27" s="3">
         <v>20100</v>
       </c>
       <c r="AJ27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-51100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>15400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2902,8 +2960,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2973,8 +3034,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
@@ -2991,14 +3052,14 @@
       <c r="AE29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG29" s="3">
         <v>300</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-28100</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>10</v>
@@ -3012,8 +3073,11 @@
       <c r="AL29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3122,8 +3186,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3232,228 +3299,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>10</v>
+      <c r="D32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>10500</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3">
         <v>7000</v>
       </c>
-      <c r="H32" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>10</v>
+      <c r="I32" s="3">
+        <v>6500</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>3800</v>
       </c>
       <c r="W32" s="3">
         <v>3800</v>
       </c>
       <c r="X32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y32" s="3">
         <v>4100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>800</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>1400</v>
       </c>
       <c r="AI32" s="3">
         <v>1400</v>
       </c>
       <c r="AJ32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AK32" s="3">
         <v>1700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E33" s="3">
         <v>58000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>37500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>33800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>38400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>20400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>31200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>41000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>29400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>32900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>33200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>23200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>14900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>31900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>48100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>17600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>29900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>37500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>20800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>18300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>18700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>11900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AH33" s="3">
-        <v>20100</v>
       </c>
       <c r="AI33" s="3">
         <v>20100</v>
       </c>
       <c r="AJ33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-51100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>15400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3562,233 +3638,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E35" s="3">
         <v>58000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>37500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>33800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>38400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>20400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>31200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>41000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>29400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>32900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>33200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>23200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>14900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>31900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>48100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>17600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>29900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>37500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>20800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>18300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>18700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>11900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AH35" s="3">
-        <v>20100</v>
       </c>
       <c r="AI35" s="3">
         <v>20100</v>
       </c>
       <c r="AJ35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-51100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>15400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44562</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44191</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43099</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3827,8 +3912,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3867,151 +3953,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>292900</v>
+      </c>
+      <c r="E41" s="3">
         <v>306800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>320800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>299300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>344400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>178800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>194000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>351000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>285700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>284500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>224000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>241200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>214900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>259500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>236900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>192400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>173500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>192300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>189000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>279200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>275700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>137300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>126400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>112000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>190200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>169400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>154900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>199800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>192100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>180200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>251600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>203600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>171700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>139600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>129600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>138900</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E42" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F42" s="3">
         <v>1700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1100</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4087,480 +4177,495 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200800</v>
+      </c>
+      <c r="E43" s="3">
         <v>202700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>211900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>213500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>201500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>206600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>211600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>174200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>177100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>179100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>181100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>171500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>146500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>159400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>155000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>141300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>132900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>127600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>146900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>141500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>141100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>165200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>170800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>176500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>163300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>185000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>167600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>161600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>151300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>151200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>146700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>143700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>151500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>152700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>150600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>360500</v>
+      </c>
+      <c r="E44" s="3">
         <v>365100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>359600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>382100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>373800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>317200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>304000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>285800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>289200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>259400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>255800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>254700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>277900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>293000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>305700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>322700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>326500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>322600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>299700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>305200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>294500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>270300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>254200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>244500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>222000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>194300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>168900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>163600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>175300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>160800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>158800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>168600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>173900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>176900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>188500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>60400</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
       <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>1900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>45500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>48400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>48500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>44100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>51500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>51100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>32700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>34400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>48100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>30800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>31200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>34700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>39800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>27400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>24400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>27900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>32200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>29000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>32600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>37500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>30900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>40900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>27900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>913200</v>
+      </c>
+      <c r="E46" s="3">
         <v>935000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1005900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>955900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>978600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>768900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>765000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>865700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>801600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>769700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>706300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>715800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>687800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>756000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>729500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>699200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>684400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>693500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>668300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>760300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>759400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>603600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>582600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>567800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>615300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>576100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>515900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>552800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>551000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>521200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>589700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>553400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>528100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>510000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>496600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>512400</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="3">
-        <v>4100</v>
-      </c>
-      <c r="F47" s="3" t="s">
+      <c r="H47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I47" s="3">
+        <v>100</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G47" s="3">
-        <v>7600</v>
-      </c>
-      <c r="H47" s="3">
-        <v>100</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>500</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4637,228 +4742,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>284100</v>
+        <v>286900</v>
       </c>
       <c r="E48" s="3">
+        <v>331500</v>
+      </c>
+      <c r="F48" s="3">
         <v>286100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>300500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>302500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>366600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>318700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>307800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>304500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>364300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>313100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>307800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>288300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>258500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>238800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>223700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>214800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>217600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>240000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>240400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>243000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>305600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>322300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>264200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>276700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>344000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>351100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>344600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>315900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>332200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>330000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>320200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>322000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>323900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>336000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1060000</v>
+        <v>1057900</v>
       </c>
       <c r="E49" s="3">
+        <v>1104000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1070900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1104000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1108300</v>
       </c>
-      <c r="H49" s="3">
-        <v>971200</v>
-      </c>
       <c r="I49" s="3">
+        <v>994100</v>
+      </c>
+      <c r="J49" s="3">
         <v>984300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>715900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>734100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>742000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>750500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>757600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>768800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>777500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>792200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>805800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>820000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>831900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>335200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>341800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>354800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>343800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>318400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>324600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>331500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>338500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>345400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>352300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>359600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>368000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>375000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>380500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>384400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>388400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>452700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4967,8 +5081,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5077,118 +5194,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>171900</v>
+        <v>183400</v>
       </c>
       <c r="E52" s="3">
+        <v>71600</v>
+      </c>
+      <c r="F52" s="3">
         <v>156300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>155800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>134700</v>
       </c>
-      <c r="H52" s="3">
-        <v>81100</v>
-      </c>
       <c r="I52" s="3">
+        <v>58200</v>
+      </c>
+      <c r="J52" s="3">
         <v>127400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>116600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>117300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>53600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>108100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>83900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>75600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>67700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>70900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>72700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>75000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>76900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>74500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>75700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>76000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>14100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>14500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>33900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>36100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>16200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>15200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>14600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>16000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>16900</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>17000</v>
       </c>
       <c r="AI52" s="3">
         <v>17000</v>
       </c>
       <c r="AJ52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AK52" s="3">
         <v>16400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>21200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5297,118 +5420,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2462100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2450900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2531300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2525200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2541000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2195600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2200400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2011300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1962300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1934800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1878100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1865100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1820500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1859700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1831400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1801500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1794200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1819900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1318100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1418200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1433200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1267100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1237700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1190500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1259600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1274800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1227600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1265700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1241200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1237300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1311700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1271200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1251400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1238700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1306400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1334800</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5447,8 +5576,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5487,668 +5617,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>10</v>
+      <c r="D57" s="3">
+        <v>46000</v>
       </c>
       <c r="E57" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F57" s="3">
         <v>63000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>69200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>76900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>73400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>56800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>80200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>78100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>63800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>61500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>57900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>58400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>51200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>45000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>49100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>50300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>43000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>49100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>48500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>50700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>52300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>57400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>60800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>63400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>62600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>57900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>65400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>55300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>41500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>41800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>39400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>43000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>48800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>303600</v>
+        <v>303900</v>
       </c>
       <c r="E58" s="3">
+        <v>311700</v>
+      </c>
+      <c r="F58" s="3">
         <v>5100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>18400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13700</v>
-      </c>
-      <c r="J58" s="3">
-        <v>13600</v>
       </c>
       <c r="K58" s="3">
         <v>13600</v>
       </c>
       <c r="L58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="M58" s="3">
         <v>18900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>58200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>214100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>144100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>82700</v>
-      </c>
-      <c r="S58" s="3">
-        <v>17000</v>
       </c>
       <c r="T58" s="3">
         <v>17000</v>
       </c>
       <c r="U58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="V58" s="3">
         <v>17100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>167000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>231400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>77000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>62000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>56900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>117500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>27700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>17200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>12700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>194300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>151500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>108600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>65900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>61000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>66300</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>274600</v>
+        <v>145600</v>
       </c>
       <c r="E59" s="3">
+        <v>140000</v>
+      </c>
+      <c r="F59" s="3">
         <v>139200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>150000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>137300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>128000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>132400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>124900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>112300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>104500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>153200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>142500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>115700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>169700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>160200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>160800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>162200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>186200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>134400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>122500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>128000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>147100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>142400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>125700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>115300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>144700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>131500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>118600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>111600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>135200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>131200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>104600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>100300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>107200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>101100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>531400</v>
+      </c>
+      <c r="E60" s="3">
         <v>578100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>253200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>273900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>260100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>300400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>261800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>264200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>236900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>251800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>226900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>262200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>180500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>442300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>355400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>288500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>228300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>253500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>194400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>338600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>407800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>274800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>256700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>240100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>293700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>235800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>211300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>189200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>194000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>384700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>324200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>255000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>205500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>211200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>216200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1052000</v>
+        <v>921300</v>
       </c>
       <c r="E61" s="3">
+        <v>971700</v>
+      </c>
+      <c r="F61" s="3">
         <v>1288300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1309500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1291600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>855500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>857300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>748700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>751400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>811800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>756800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>759600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>763100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>559400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>633100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>698000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>767300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>690600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>292700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>297000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>296900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>305500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>309700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>314000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>318100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>322500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>326600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>331000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>330800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>59400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>118700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>178000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>237200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>253600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>270000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F62" s="3">
+        <v>21400</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="3">
-        <v>21400</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>19100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>75800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>69900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>72000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>17000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>118400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>114400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>106500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>108600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>112100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>116400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>121400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>144200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>111800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>114700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>119900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>99700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>96700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>52700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>56800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>48700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>46600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>44200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>42300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>40800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>46000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>36900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>35900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>34300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>49300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6257,8 +6406,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6367,8 +6519,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6477,118 +6632,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1579800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1630100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1624400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1646400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1635600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1235600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1257100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1117600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1097600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1116800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1102100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1136100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1050100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1110300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1100600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1102900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1117100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1088300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>598900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>750300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>824600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>680000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>663200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>606800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>668600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>606900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>584500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>564400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>567100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>484900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>488900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>469900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>478600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>499100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>535500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>585700</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6627,8 +6788,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6737,8 +6899,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6847,8 +7012,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6957,8 +7125,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7067,118 +7238,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>10</v>
+      <c r="D72" s="3">
+        <v>356000</v>
       </c>
       <c r="E72" s="3">
+        <v>352200</v>
+      </c>
+      <c r="F72" s="3">
         <v>392200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>368500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>386600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>360500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>340100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>308900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>284000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>253200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>223800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>204400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>222300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>202400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>192700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>169400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>154600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>158000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>169000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>137100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>89000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>78500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>69900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>85600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>99400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>161400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>140600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>194400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>189900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>266900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>323600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>330200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>310100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>289900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>341100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>325700</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7287,8 +7464,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7397,8 +7577,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7507,118 +7690,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>882300</v>
+      </c>
+      <c r="E76" s="3">
         <v>820800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>906900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>878900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>905400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>960000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>943300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>893700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>864600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>818000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>776000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>729000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>770400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>749400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>730800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>698500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>677100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>731700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>719200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>667900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>608600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>587100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>574600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>583800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>591000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>667900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>643100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>701300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>674100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>752400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>822800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>801300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>772800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>739600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>770900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7727,233 +7916,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44562</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44191</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43099</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E81" s="3">
         <v>58000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>37500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>33800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>38400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>20400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>31200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>41000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>29400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>32900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>33200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>23200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>14900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>31900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>48100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>17600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>29900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>37500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>20800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>18300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>18700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>11900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AH81" s="3">
-        <v>20100</v>
       </c>
       <c r="AI81" s="3">
         <v>20100</v>
       </c>
       <c r="AJ81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-51100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>15400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7992,118 +8190,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E83" s="3">
         <v>14700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>22400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>23500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>25000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>21900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>20800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>28800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>27100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>27000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>27400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>29800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>27900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>25300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>26400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>23000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>22300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>22200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>21800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>22200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>22300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8212,8 +8414,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8322,8 +8527,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8432,8 +8640,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8542,8 +8753,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8652,118 +8866,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E89" s="3">
         <v>116600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>43800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>48800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>64100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>99100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>79600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>64400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>87000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>42000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>68100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>62400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>43500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>66300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>29200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>46400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>79300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>29900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>20600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>58200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>57400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>23100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>57600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>65400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>58900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>38400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>34600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>55200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8802,118 +9022,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3000</v>
+        <v>-3800</v>
       </c>
       <c r="E91" s="3">
-        <v>-14400</v>
+        <v>-15600</v>
       </c>
       <c r="F91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G91" s="3">
         <v>-12000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-9900</v>
-      </c>
       <c r="H91" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="J91" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="L91" s="3">
         <v>-9700</v>
       </c>
-      <c r="I91" s="3">
-        <v>-22300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-24700</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-9700</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-45500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-20400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-48500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9022,8 +9246,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9132,118 +9359,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E94" s="3">
         <v>18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-139200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-268900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-18000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-31100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-58200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-429100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>37100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-23900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-45100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>6000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>1900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-27600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-26300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-14600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9282,8 +9515,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9314,8 +9548,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9392,8 +9626,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9502,8 +9739,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9612,8 +9852,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9722,334 +9965,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-151500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-74800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>333700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-63500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>109400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-49700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-25700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-23400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>432800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-149900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-64300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>149000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>11400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-46200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-112500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>16100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>7000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-76200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>18700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>8300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-12700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-10400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>1500</v>
       </c>
       <c r="W101" s="3">
         <v>1500</v>
       </c>
       <c r="X101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-45100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>165600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-157000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>65300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>60500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-44500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>22600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>44500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>19000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-90200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>138400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>10900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-78200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>20900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>7700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>11900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>48000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>31900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>32200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>9900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>20600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>HAE</t>
   </si>
@@ -656,513 +656,525 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44562</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44191</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43827</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43463</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>339000</v>
+      </c>
+      <c r="E8" s="3">
         <v>327300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>321400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>330600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>348500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>345500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>336200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>343300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>336300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>318200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>311300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>304400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>305300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>297500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>261500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>265000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>259800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>239900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>228500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>225000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>240400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>209500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>195600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>238500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>259000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>252600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>238500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>249300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>247400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>241600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>229300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>233600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>234000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>225400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>211000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>228100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>227800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E9" s="3">
         <v>132700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>129500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>131400</v>
       </c>
-      <c r="G9" s="3">
-        <v>148600</v>
-      </c>
       <c r="H9" s="3">
+        <v>152000</v>
+      </c>
+      <c r="I9" s="3">
         <v>154300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>156900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>154300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>151300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>147600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>143900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>140200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>146600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>139600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>119400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>128700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>121400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>117100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>118200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>143100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>120200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>104000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>105000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>124900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>130900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>125600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>122500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>138100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>136200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>129700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>124900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>129200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>122700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>120800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>119300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>146000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>126800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>202300</v>
+      </c>
+      <c r="E10" s="3">
         <v>194600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>191900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>199200</v>
       </c>
-      <c r="G10" s="3">
-        <v>199900</v>
-      </c>
       <c r="H10" s="3">
+        <v>196600</v>
+      </c>
+      <c r="I10" s="3">
         <v>191200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>179300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>188900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>184900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>170600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>167500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>164300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>158700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>157900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>142100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>136300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>138400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>122800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>110300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>82000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>120200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>105500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>90600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>113600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>128100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>127000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>116000</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>111200</v>
       </c>
       <c r="AE10" s="3">
         <v>111200</v>
       </c>
       <c r="AF10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="AG10" s="3">
         <v>111900</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>104400</v>
       </c>
       <c r="AH10" s="3">
         <v>104400</v>
       </c>
       <c r="AI10" s="3">
+        <v>104400</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>111300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>104600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>91700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>82100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>101000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1203,124 +1215,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E12" s="3">
         <v>14500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>15600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12700</v>
-      </c>
-      <c r="P12" s="3">
-        <v>10900</v>
       </c>
       <c r="Q12" s="3">
         <v>10900</v>
       </c>
       <c r="R12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="S12" s="3">
         <v>13200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>8700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>11100</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>7500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>8200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>9300</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>8500</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1435,186 +1451,192 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E14" s="3">
         <v>10300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>11100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-27100</v>
       </c>
-      <c r="G14" s="3">
-        <v>7100</v>
-      </c>
       <c r="H14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I14" s="3">
         <v>8100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>19500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>11000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>16600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-1200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-31600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>10300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>51700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>24500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>4400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>31700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>5200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>57200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>400</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E15" s="3">
         <v>11200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>12200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>11500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>11400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>12400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>32800</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>10</v>
@@ -1628,8 +1650,8 @@
       <c r="AA15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1667,8 +1689,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1706,240 +1731,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>267800</v>
+      </c>
+      <c r="E17" s="3">
         <v>258500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>256500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>273700</v>
       </c>
-      <c r="G17" s="3">
-        <v>282400</v>
-      </c>
       <c r="H17" s="3">
+        <v>285800</v>
+      </c>
+      <c r="I17" s="3">
         <v>285700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>285200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>293900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>277300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>275600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>257700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>258200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>262000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>250800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>230700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>245800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>224100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>215400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>227100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>246200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>199900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>150700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>183900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>212500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>218100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>202800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>251800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>225400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>219000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>215500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>224100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>219300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>233000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>201100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>186300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>285600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>206600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E18" s="3">
         <v>68800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>64900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>56900</v>
       </c>
-      <c r="G18" s="3">
-        <v>66100</v>
-      </c>
       <c r="H18" s="3">
+        <v>62800</v>
+      </c>
+      <c r="I18" s="3">
         <v>59800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>51000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>49400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>59000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>42600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>53600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>46300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>43300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>46700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>30800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>35700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>24500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-21200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>40500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>58800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>26000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>40900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>49800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>23900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>28400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>26100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>14300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>24300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>24700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-57500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>21200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1980,278 +2012,285 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>7200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
-        <v>-10500</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>10</v>
+      <c r="G20" s="3">
+        <v>7400</v>
       </c>
       <c r="H20" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I20" s="3">
         <v>7000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6500</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-3800</v>
       </c>
       <c r="Y20" s="3">
         <v>-3800</v>
       </c>
       <c r="Z20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>-1400</v>
       </c>
       <c r="AK20" s="3">
         <v>-1400</v>
       </c>
       <c r="AL20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>84400</v>
+      </c>
+      <c r="E21" s="3">
         <v>72800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>71700</v>
       </c>
-      <c r="F21" s="3">
-        <v>78700</v>
-      </c>
       <c r="G21" s="3">
-        <v>78300</v>
+        <v>60800</v>
       </c>
       <c r="H21" s="3">
+        <v>70500</v>
+      </c>
+      <c r="I21" s="3">
         <v>65000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>70400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>66300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>65900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>49800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>59100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>52600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>65800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>64500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>47900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>40100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>55800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>43500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>25000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>58100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>75800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>28700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>50700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>64900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>72100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>51600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>53400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>48300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>29700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>36300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>22500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>45100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>45000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>41200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4100</v>
       </c>
-      <c r="F22" s="3">
-        <v>23700</v>
-      </c>
       <c r="G22" s="3">
-        <v>9100</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>10</v>
+        <v>5800</v>
+      </c>
+      <c r="H22" s="3">
+        <v>4600</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="3">
         <v>13000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2500</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>10</v>
@@ -2268,11 +2307,11 @@
       <c r="T22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V22" s="3">
         <v>3000</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>10</v>
@@ -2289,8 +2328,8 @@
       <c r="AA22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2328,240 +2367,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E23" s="3">
         <v>51300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>45200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>70700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>49900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>44700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>46700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>44000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>32800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>51600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>32600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>42200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>41100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>25500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>15300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>31400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>19900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-27400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>37400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>55000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>22000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>37800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>45100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-17700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>21800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>25500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>23000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>13300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>22900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>23300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-59200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>18900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E24" s="3">
         <v>12600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7900</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>5600</v>
       </c>
       <c r="R24" s="3">
         <v>5600</v>
       </c>
       <c r="S24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="T24" s="3">
         <v>8200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-16400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-21300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>3500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2676,240 +2724,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E26" s="3">
         <v>38700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>34000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>58000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>37500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>33800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>38400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>31200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>41000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>29400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>32900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>33200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>23200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>14900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>31900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>48100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>10500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>17600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>29900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>37500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>20800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>18300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>18700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>11600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>21600</v>
-      </c>
-      <c r="AJ26" s="3">
-        <v>20100</v>
       </c>
       <c r="AK26" s="3">
         <v>20100</v>
       </c>
       <c r="AL26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AM26" s="3">
         <v>-51100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>15400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E27" s="3">
         <v>38700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>34000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>58000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>33800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>38400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>31200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>41000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>32900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>33200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>23200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>14900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>31900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>48100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>17600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>29900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>37500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>20800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>18300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>18700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>11600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>21600</v>
-      </c>
-      <c r="AJ27" s="3">
-        <v>20100</v>
       </c>
       <c r="AK27" s="3">
         <v>20100</v>
       </c>
       <c r="AL27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AM27" s="3">
         <v>-51100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>15400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3024,8 +3081,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3101,8 +3161,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>10</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>10</v>
@@ -3119,14 +3179,14 @@
       <c r="AG29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI29" s="3">
         <v>300</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-28100</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>10</v>
@@ -3140,8 +3200,11 @@
       <c r="AN29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3256,8 +3319,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3372,240 +3438,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
-        <v>10500</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>10</v>
+      <c r="G32" s="3">
+        <v>-7400</v>
       </c>
       <c r="H32" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-7000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6500</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>3800</v>
       </c>
       <c r="Y32" s="3">
         <v>3800</v>
       </c>
       <c r="Z32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA32" s="3">
         <v>4100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>800</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>1400</v>
       </c>
       <c r="AK32" s="3">
         <v>1400</v>
       </c>
       <c r="AL32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AM32" s="3">
         <v>1700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>2200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E33" s="3">
         <v>38700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>34000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>58000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>37500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>33800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>38400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>31200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>41000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>29400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>33200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>23200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>14900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>31900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>48100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>17600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>29900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>37500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>20800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>18300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>18700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>11900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AJ33" s="3">
-        <v>20100</v>
       </c>
       <c r="AK33" s="3">
         <v>20100</v>
       </c>
       <c r="AL33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AM33" s="3">
         <v>-51100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>15400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3720,245 +3795,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E35" s="3">
         <v>38700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>34000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>58000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>37500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>33800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>38400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>31200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>41000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>29400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>33200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>23200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>14900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>31900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>48100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>17600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>29900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>37500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>20800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>18300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>18700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>11900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AJ35" s="3">
-        <v>20100</v>
       </c>
       <c r="AK35" s="3">
         <v>20100</v>
       </c>
       <c r="AL35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AM35" s="3">
         <v>-51100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>15400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44562</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44191</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43827</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43463</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3999,8 +4083,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4041,163 +4126,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>363400</v>
+      </c>
+      <c r="E41" s="3">
         <v>296400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>292900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>306800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>320800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>299300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>344400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>178800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>194000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>351000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>285700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>284500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>224000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>241200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>214900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>259500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>236900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>192400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>173500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>192300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>189000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>279200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>275700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>137300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>126400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>112000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>190200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>169400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>154900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>199800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>192100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>180200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>251600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>203600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>171700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>139600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>129600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>138900</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>200</v>
+      </c>
+      <c r="E42" s="3">
         <v>600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1100</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4273,510 +4362,525 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>195700</v>
+      </c>
+      <c r="E43" s="3">
         <v>207100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>202700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>211900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>213500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>201500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>206600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>211600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>174200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>177100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>179100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>181100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>171500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>146500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>159400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>155000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>141300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>132900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>127600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>146900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>141500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>141100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>165200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>170800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>176500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>163300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>185000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>167600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>161600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>151300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>151200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>146700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>143700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>151500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>152700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>150600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>321200</v>
+      </c>
+      <c r="E44" s="3">
         <v>336200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>360500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>365100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>359600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>382100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>373800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>317200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>304000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>285800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>289200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>259400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>255800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>254700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>277900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>293000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>305700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>322700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>326500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>322600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>299700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>305200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>294500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>270300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>254200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>244500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>222000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>194300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>168900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>163600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>175300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>160800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>158800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>168600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>173900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>176900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>188500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>45500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>48400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>44100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>31900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>42900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>51500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>32700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>34400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>48100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>30800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>31200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>34700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>39800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>27400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>24400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>27900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>32200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>29000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>32600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>37500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>30900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>40900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>27900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>943700</v>
+      </c>
+      <c r="E46" s="3">
         <v>899700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>913200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>935000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1005900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>955900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>978600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>768900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>765000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>865700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>801600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>769700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>706300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>715800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>687800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>756000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>729500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>699200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>684400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>693500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>668300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>760300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>759400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>603600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>582600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>567800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>615300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>576100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>515900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>552800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>551000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>521200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>589700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>553400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>528100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>510000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>496600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>512400</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="3">
+        <v>97200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>88600</v>
+      </c>
+      <c r="F47" s="3">
+        <v>12900</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H47" s="3">
+        <v>39100</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="3">
-        <v>12900</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H47" s="3" t="s">
+      <c r="J47" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K47" s="3">
+        <v>100</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I47" s="3">
-        <v>7600</v>
-      </c>
-      <c r="J47" s="3">
-        <v>100</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>500</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4853,240 +4957,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>297200</v>
+      </c>
+      <c r="E48" s="3">
         <v>292500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>286900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>331500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>286100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>300500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>302500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>366600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>318700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>307800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>304500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>364300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>313100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>307800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>288300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>258500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>238800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>223700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>214800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>217600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>240000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>240400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>243000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>305600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>322300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>264200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>276700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>344000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>351100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>344600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>315900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>332200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>330000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>320200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>322000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>323900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>336000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1026600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1034500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1057900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1104000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1070900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1104000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1108300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>994100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>984300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>715900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>734100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>742000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>750500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>757600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>768800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>777500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>792200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>805800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>820000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>831900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>335200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>341800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>354800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>343800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>318400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>324600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>331500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>338500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>345400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>352300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>359600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>368000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>375000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>380500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>384400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>388400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>452700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5201,8 +5314,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5317,124 +5433,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>208000</v>
+        <v>118900</v>
       </c>
       <c r="E52" s="3">
+        <v>119400</v>
+      </c>
+      <c r="F52" s="3">
         <v>183400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>71600</v>
       </c>
-      <c r="G52" s="3">
-        <v>156300</v>
-      </c>
       <c r="H52" s="3">
+        <v>121300</v>
+      </c>
+      <c r="I52" s="3">
         <v>155800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>134700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>58200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>127400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>116600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>117300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>53600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>108100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>83900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>75600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>67700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>70900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>72700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>75000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>76900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>74500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>75700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>76000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>14100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>33900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>36100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>15200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>16000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>14600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>16000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>16900</v>
-      </c>
-      <c r="AJ52" s="3">
-        <v>17000</v>
       </c>
       <c r="AK52" s="3">
         <v>17000</v>
       </c>
       <c r="AL52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AM52" s="3">
         <v>16400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>21200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5549,124 +5671,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2490900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2442200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2462100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2450900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2531300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2525200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2541000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2195600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2200400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2011300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1962300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1934800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1878100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1865100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1820500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1859700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1831400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1801500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1794200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1819900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1318100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1418200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1433200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1267100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1237700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1190500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1259600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1274800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1227600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1265700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1241200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1237300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1311700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1271200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1251400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1238700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1306400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1334800</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5707,8 +5835,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5749,704 +5878,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E57" s="3">
         <v>61700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>46000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>63000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>69200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>76900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>73400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>56800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>80200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>78100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>63900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>63800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>61500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>57900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>58400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>51200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>45000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>49100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>50300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>43000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>49100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>48500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>50700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>52300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>57400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>60800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>63400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>62600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>57900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>65400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>55300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>41500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>41800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>39400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>43000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>48800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>304700</v>
+      </c>
+      <c r="E58" s="3">
         <v>304300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>303900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>311700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13700</v>
-      </c>
-      <c r="L58" s="3">
-        <v>13600</v>
       </c>
       <c r="M58" s="3">
         <v>13600</v>
       </c>
       <c r="N58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="O58" s="3">
         <v>18900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>58200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>214100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>144100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>82700</v>
-      </c>
-      <c r="U58" s="3">
-        <v>17000</v>
       </c>
       <c r="V58" s="3">
         <v>17000</v>
       </c>
       <c r="W58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="X58" s="3">
         <v>17100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>167000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>231400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>77000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>62000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>56900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>117500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>27700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>12700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>17000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>194300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>151500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>108600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>65900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>61000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>66300</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E59" s="3">
         <v>134000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>145600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>140000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>139200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>150000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>137300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>128000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>132400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>124900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>112300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>104500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>153200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>142500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>115700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>169700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>160200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>160800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>162200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>186200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>134400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>122500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>128000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>147100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>142400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>125700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>115300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>144700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>131500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>118600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>111600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>135200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>131200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>104600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>100300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>107200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>101100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>539900</v>
+      </c>
+      <c r="E60" s="3">
         <v>548300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>531400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>578100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>253200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>273900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>260100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>300400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>261800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>264200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>236900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>251800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>226900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>262200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>180500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>442300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>355400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>288500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>228300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>253500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>194400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>338600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>407800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>274800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>256700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>240100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>293700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>235800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>211300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>189200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>194000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>384700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>324200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>255000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>205500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>211200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>216200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>920300</v>
+      </c>
+      <c r="E61" s="3">
         <v>920800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>921300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>971700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1288300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1309500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1291600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>855500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>857300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>748700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>751400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>811800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>756800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>759600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>763100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>559400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>633100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>698000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>767300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>690600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>292700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>297000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>296900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>305500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>309700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>314000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>318100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>322500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>326600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>331000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>330800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>59400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>118700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>178000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>237200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>253600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>270000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E62" s="3">
         <v>65600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>67600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>17700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21400</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="I62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>75800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>69900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>72000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>118400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>114400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>106500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>108600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>112100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>116400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>121400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>144200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>111800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>114700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>119900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>99700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>96700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>52700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>56800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>48700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>46600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>44200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>42300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>40800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>46000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>36900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>35900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>34300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>49300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6561,8 +6709,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6677,8 +6828,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6793,124 +6947,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1579400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1593000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1579800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1630100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1624400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1646400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1635600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1235600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1257100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1117600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1097600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1116800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1102100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1136100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1050100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1110300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1100600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1102900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1117100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1088300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>598900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>750300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>824600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>680000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>663200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>606800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>668600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>606900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>584500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>564400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>567100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>484900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>488900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>469900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>478600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>499100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>535500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>585700</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6951,8 +7111,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7067,8 +7228,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7183,8 +7347,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7299,8 +7466,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7415,124 +7585,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>381100</v>
+      </c>
+      <c r="E72" s="3">
         <v>336300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>356000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>352200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>392200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>368500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>386600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>360500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>340100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>308900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>284000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>253200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>223800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>204400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>222300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>202400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>192700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>169400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>154600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>158000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>169000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>137100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>89000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>78500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>69900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>85600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>99400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>161400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>140600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>194400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>189900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>266900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>323600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>330200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>310100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>289900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>341100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>325700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7647,8 +7823,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7763,8 +7942,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7879,124 +8061,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>911500</v>
+      </c>
+      <c r="E76" s="3">
         <v>849200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>882300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>820800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>906900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>878900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>905400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>960000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>943300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>893700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>864600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>818000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>776000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>729000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>770400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>749400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>730800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>698500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>677100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>731700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>719200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>667900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>608600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>587100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>574600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>583800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>591000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>667900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>643100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>701300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>674100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>752400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>822800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>801300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>772800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>739600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>770900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8111,245 +8299,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44562</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44191</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43827</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43463</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E81" s="3">
         <v>38700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>34000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>58000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>37500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>33800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>38400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>31200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>41000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>29400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>33200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>23200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>14900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>31900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>48100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>17600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>29900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>37500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>20800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>18300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>18700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>11900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AJ81" s="3">
-        <v>20100</v>
       </c>
       <c r="AK81" s="3">
         <v>20100</v>
       </c>
       <c r="AL81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AM81" s="3">
         <v>-51100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>15400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8390,124 +8587,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E83" s="3">
         <v>15000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14200</v>
       </c>
-      <c r="H83" s="3">
-        <v>11400</v>
-      </c>
       <c r="I83" s="3">
-        <v>15400</v>
+        <v>13500</v>
       </c>
       <c r="J83" s="3">
+        <v>13300</v>
+      </c>
+      <c r="K83" s="3">
         <v>13500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>22400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>23500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>21900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>28800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>27100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>27000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>27400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>29800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>27900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>25300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>26400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>23000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>22300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>22200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>21800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>22200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>22300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8622,8 +8823,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8738,8 +8942,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8854,8 +9061,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8970,8 +9180,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9086,124 +9299,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E89" s="3">
         <v>111300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>116600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>43800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>48800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-27400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>64100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>99100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>79600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>64400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>87000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>42000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>68100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>62400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>43500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>66300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>29200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>46400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>79300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>29900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>20600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>58200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>57400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>23100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>57600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>65400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>58900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>38400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>34600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>55200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9244,124 +9463,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-34200</v>
+        <v>-6300</v>
       </c>
       <c r="E91" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15600</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1800</v>
-      </c>
       <c r="H91" s="3">
-        <v>-16200</v>
+        <v>-8500</v>
       </c>
       <c r="I91" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J91" s="3">
         <v>-5700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-24700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-45500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-35100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-48500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9476,8 +9699,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9592,124 +9818,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>18000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-139200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-268900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-25100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-36500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-58200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-34500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-429100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>37100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-23900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-45100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-19900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>6000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-13200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-27600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-26300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-14600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9750,8 +9982,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9788,8 +10021,8 @@
       <c r="N96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9866,8 +10099,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9982,8 +10218,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10098,8 +10337,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10214,352 +10456,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-76600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-151500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-74800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>333700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-63500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>109400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-49700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-23400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>432800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-149900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-64300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>149000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>11400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-112500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>16100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>7000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-76200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>18700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-12700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-10400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E101" s="3">
         <v>4200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3100</v>
-      </c>
-      <c r="X101" s="3">
-        <v>1500</v>
       </c>
       <c r="Y101" s="3">
         <v>1500</v>
       </c>
       <c r="Z101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E102" s="3">
         <v>3500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>21600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-45100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>165600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-157000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>65300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>60500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>26300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-44500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>22600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>44500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-90200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>138400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>10900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>14400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-78200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>20900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>14500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>7700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>11900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>31900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>32200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>9900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>20600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>HAE</t>
   </si>
@@ -656,525 +656,538 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>46018</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45654</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45290</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44562</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44191</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43827</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43736</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43645</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43554</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43463</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43372</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43099</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42917</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42826</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>346400</v>
+      </c>
+      <c r="E8" s="3">
         <v>339000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>327300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>321400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>330600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>348500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>345500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>336200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>343300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>336300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>318200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>311300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>304400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>305300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>297500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>261500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>265000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>259800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>239900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>228500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>225000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>240400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>209500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>195600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>238500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>259000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>252600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>238500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>249300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>247400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>241600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>229300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>233600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>234000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>225400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>211000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>228100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>227800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>220300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>148100</v>
+      </c>
+      <c r="E9" s="3">
         <v>136600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>132700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>129500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>131400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>152000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>154300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>156900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>154300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>151300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>147600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>143900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>140200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>146600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>139600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>119400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>128700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>121400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>117100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>118200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>143100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>120200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>104000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>105000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>124900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>130900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>125600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>122500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>138100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>136200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>129700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>124900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>129200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>122700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>120800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>119300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>146000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>126800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>116000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>198300</v>
+      </c>
+      <c r="E10" s="3">
         <v>202300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>194600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>191900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>199200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>196600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>191200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>179300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>188900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>184900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>170600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>167500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>164300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>158700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>157900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>142100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>136300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>138400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>122800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>110300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>82000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>120200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>105500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>90600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>113600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>128100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>127000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>116000</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>111200</v>
       </c>
       <c r="AF10" s="3">
         <v>111200</v>
       </c>
       <c r="AG10" s="3">
+        <v>111200</v>
+      </c>
+      <c r="AH10" s="3">
         <v>111900</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>104400</v>
       </c>
       <c r="AI10" s="3">
         <v>104400</v>
       </c>
       <c r="AJ10" s="3">
+        <v>104400</v>
+      </c>
+      <c r="AK10" s="3">
         <v>111300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>104600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>91700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>82100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>101000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>104300</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1216,127 +1229,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E12" s="3">
         <v>14300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15600</v>
       </c>
-      <c r="G12" s="3">
-        <v>14300</v>
-      </c>
       <c r="H12" s="3">
+        <v>16700</v>
+      </c>
+      <c r="I12" s="3">
         <v>15800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12700</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>10900</v>
       </c>
       <c r="R12" s="3">
         <v>10900</v>
       </c>
       <c r="S12" s="3">
+        <v>10900</v>
+      </c>
+      <c r="T12" s="3">
         <v>13200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>8500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>8700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>8600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>9400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>12400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>7500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>8200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>9300</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>8500</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1454,192 +1471,198 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E14" s="3">
         <v>3800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-27100</v>
-      </c>
       <c r="H14" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="I14" s="3">
         <v>3800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>19500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>11000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>16600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-31600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>10300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>51700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>6400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>24500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>31700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>5200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>57200</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>400</v>
       </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E15" s="3">
         <v>10900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>8400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>11500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>12200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>11400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>12400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>32800</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>10</v>
@@ -1653,8 +1676,8 @@
       <c r="AB15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1692,8 +1715,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1732,246 +1758,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>298300</v>
+      </c>
+      <c r="E17" s="3">
         <v>267800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>258500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>256500</v>
       </c>
-      <c r="G17" s="3">
-        <v>273700</v>
-      </c>
       <c r="H17" s="3">
+        <v>275100</v>
+      </c>
+      <c r="I17" s="3">
         <v>285800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>285700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>285200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>293900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>277300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>275600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>257700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>258200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>262000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>250800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>230700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>245800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>224100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>215400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>227100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>246200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>199900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>150700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>183900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>212500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>218100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>202800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>251800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>225400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>219000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>215500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>224100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>219300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>233000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>201100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>186300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>285600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>206600</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>195500</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E18" s="3">
         <v>71200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>68800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>64900</v>
       </c>
-      <c r="G18" s="3">
-        <v>56900</v>
-      </c>
       <c r="H18" s="3">
+        <v>55500</v>
+      </c>
+      <c r="I18" s="3">
         <v>62800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>59800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>51000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>49400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>59000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>42600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>53600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>43300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>46700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>30800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>19200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>35700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>24500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-21200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>40500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>58800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>26000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>40900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>49800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>23900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>28400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>26100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>5200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>24300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>24700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-57500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>21200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2013,287 +2046,294 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4600</v>
       </c>
-      <c r="G20" s="3">
-        <v>7400</v>
-      </c>
       <c r="H20" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="I20" s="3">
         <v>4500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6500</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-3800</v>
       </c>
       <c r="Z20" s="3">
         <v>-3800</v>
       </c>
       <c r="AA20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-800</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>-1400</v>
       </c>
       <c r="AL20" s="3">
         <v>-1400</v>
       </c>
       <c r="AM20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-2200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E21" s="3">
         <v>84400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>72800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>71700</v>
       </c>
-      <c r="G21" s="3">
-        <v>60800</v>
-      </c>
       <c r="H21" s="3">
+        <v>85500</v>
+      </c>
+      <c r="I21" s="3">
         <v>70500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>65000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>70400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>66300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>65900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>49800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>59100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>52600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>65800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>64500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>47900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>40100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>55800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>43500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>25000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>58100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>75800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>28700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>50700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>64900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>72100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>51600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>53400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>48300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>29700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>36300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>22500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>45100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>45000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-37000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>41200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E22" s="3">
         <v>9700</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4100</v>
       </c>
-      <c r="G22" s="3">
-        <v>5800</v>
-      </c>
       <c r="H22" s="3">
+        <v>19300</v>
+      </c>
+      <c r="I22" s="3">
         <v>4600</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
         <v>13000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2500</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1000</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>10</v>
@@ -2310,11 +2350,11 @@
       <c r="U22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W22" s="3">
         <v>3000</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>10</v>
@@ -2331,8 +2371,8 @@
       <c r="AB22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2370,246 +2410,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E23" s="3">
         <v>60000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>51300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>45200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>70700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>49900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>44700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>46700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>44000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>32800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>51600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>32600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>42200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>41100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>25500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>15300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>31400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>19900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-27400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>37400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>55000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>22000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>37800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>45100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-17700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>21800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>25500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>23000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>22900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>23300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-59200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>18900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E24" s="3">
         <v>15200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>10500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7900</v>
-      </c>
-      <c r="R24" s="3">
-        <v>5600</v>
       </c>
       <c r="S24" s="3">
         <v>5600</v>
       </c>
       <c r="T24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="U24" s="3">
         <v>8200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-16400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-9200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-21300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>3500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2727,246 +2776,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E26" s="3">
         <v>44700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>38700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>58000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>37500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>33800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>38400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>31200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>41000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>29400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>32900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>23200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>14900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>31900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>48100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>10500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>17600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>29900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>37500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>18300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>18700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>11600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>21600</v>
-      </c>
-      <c r="AK26" s="3">
-        <v>20100</v>
       </c>
       <c r="AL26" s="3">
         <v>20100</v>
       </c>
       <c r="AM26" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AN26" s="3">
         <v>-51100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>15400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E27" s="3">
         <v>44700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>38700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>58000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>37500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>33800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>38400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>20400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>31200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>41000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>29400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>32900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>33200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>23200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>14900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>31900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>48100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>10500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>17600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>29900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>37500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>18300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>18700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>11600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>21600</v>
-      </c>
-      <c r="AK27" s="3">
-        <v>20100</v>
       </c>
       <c r="AL27" s="3">
         <v>20100</v>
       </c>
       <c r="AM27" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AN27" s="3">
         <v>-51100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>15400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3084,8 +3142,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3164,8 +3225,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>10</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>10</v>
@@ -3182,14 +3243,14 @@
       <c r="AH29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>300</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-28100</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>10</v>
@@ -3203,8 +3264,11 @@
       <c r="AO29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3322,8 +3386,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3441,246 +3508,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E32" s="3">
         <v>2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-7400</v>
-      </c>
       <c r="H32" s="3">
+        <v>18700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-4500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6500</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>3800</v>
       </c>
       <c r="Z32" s="3">
         <v>3800</v>
       </c>
       <c r="AA32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AB32" s="3">
         <v>4100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>800</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>1400</v>
       </c>
       <c r="AL32" s="3">
         <v>1400</v>
       </c>
       <c r="AM32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AN32" s="3">
         <v>1700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>2200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E33" s="3">
         <v>44700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>38700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>34000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>58000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>37500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>33800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>38400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>20400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>31200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>41000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>29400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>32900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>33200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>23200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>14900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>31900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>48100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>10500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>17600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>29900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>37500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>18300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>18700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AK33" s="3">
-        <v>20100</v>
       </c>
       <c r="AL33" s="3">
         <v>20100</v>
       </c>
       <c r="AM33" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AN33" s="3">
         <v>-51100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>15400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3798,251 +3874,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E35" s="3">
         <v>44700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>38700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>34000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>58000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>37500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>33800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>38400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>20400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>31200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>41000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>29400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>32900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>33200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>23200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>14900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>31900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>48100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>10500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>17600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>29900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>37500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>18300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>18700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AK35" s="3">
-        <v>20100</v>
       </c>
       <c r="AL35" s="3">
         <v>20100</v>
       </c>
       <c r="AM35" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AN35" s="3">
         <v>-51100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>15400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>46018</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45654</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45290</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44562</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44191</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43827</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43736</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43645</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43554</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43463</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43372</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43099</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42917</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42826</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4084,8 +4169,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4127,169 +4213,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>245400</v>
+      </c>
+      <c r="E41" s="3">
         <v>363400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>296400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>292900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>306800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>320800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>299300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>344400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>178800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>194000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>351000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>285700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>284500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>224000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>241200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>214900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>259500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>236900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>192400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>173500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>192300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>189000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>279200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>275700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>137300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>126400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>112000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>190200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>169400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>154900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>199800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>192100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>180200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>251600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>203600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>171700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>139600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>129600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>138900</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>800</v>
+      </c>
+      <c r="E42" s="3">
         <v>200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1100</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4365,525 +4455,540 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>216900</v>
+      </c>
+      <c r="E43" s="3">
         <v>195700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>207100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>200800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>202700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>211900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>213500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>201500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>206600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>211600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>174200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>177100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>179100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>181100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>171500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>146500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>159400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>155000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>141300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>132900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>127600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>146900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>141500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>141100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>165200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>170800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>176500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>163300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>185000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>167600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>161600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>151300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>151200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>146700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>143700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>151500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>152700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>150600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>306400</v>
+      </c>
+      <c r="E44" s="3">
         <v>321200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>336200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>360500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>365100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>359600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>382100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>373800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>317200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>304000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>285800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>289200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>259400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>255800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>254700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>277900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>293000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>305700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>322700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>326500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>322600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>299700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>305200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>294500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>270300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>254200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>244500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>222000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>194300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>168900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>163600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>175300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>160800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>158800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>168600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>173900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>176900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>188500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>45500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>48500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>44100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>42900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>51500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>51100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>32700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>34400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>48100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>30800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>31200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>34700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>39800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>27400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>24400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>27900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>32200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>29000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>32600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>37500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>30900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>40900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>27900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>834900</v>
+      </c>
+      <c r="E46" s="3">
         <v>943700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>899700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>913200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>935000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1005900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>955900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>978600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>768900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>765000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>865700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>801600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>769700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>706300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>715800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>687800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>756000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>729500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>699200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>684400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>693500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>668300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>760300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>759400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>603600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>582600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>567800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>615300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>576100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>515900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>552800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>551000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>521200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>589700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>553400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>528100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>510000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>496600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>512400</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>900</v>
+      </c>
+      <c r="E47" s="3">
         <v>97200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>88600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>39100</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>100</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>500</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4960,246 +5065,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>345400</v>
+      </c>
+      <c r="E48" s="3">
         <v>297200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>292500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>286900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>331500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>286100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>300500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>302500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>366600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>318700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>307800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>304500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>364300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>313100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>307800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>288300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>258500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>238800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>223700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>214800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>217600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>240000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>240400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>243000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>305600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>322300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>264200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>276700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>344000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>351100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>344600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>315900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>332200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>330000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>320200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>322000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>323900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>336000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1166400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1026600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1034500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1057900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1104000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1070900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1104000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1108300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>994100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>984300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>715900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>734100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>742000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>750500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>757600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>768800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>777500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>792200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>805800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>820000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>831900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>335200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>341800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>354800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>343800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>318400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>324600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>331500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>338500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>345400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>352300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>359600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>368000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>375000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>380500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>384400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>388400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>452700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>461000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5317,8 +5431,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5436,127 +5553,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E52" s="3">
         <v>118900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>119400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>183400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>71600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>121300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>155800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>134700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>58200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>127400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>116600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>117300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>53600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>108100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>83900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>75600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>67700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>70900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>72700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>75000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>76900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>74500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>75700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>76000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>14500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>33900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>36100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>16200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>15200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>16000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>14600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>16000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>16900</v>
-      </c>
-      <c r="AK52" s="3">
-        <v>17000</v>
       </c>
       <c r="AL52" s="3">
         <v>17000</v>
       </c>
       <c r="AM52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="AN52" s="3">
         <v>16400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>21200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>21600</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5674,127 +5797,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2395900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2490900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2442200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2462100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2450900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2531300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2525200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2541000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2195600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2200400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2011300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1962300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1934800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1878100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1865100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1820500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1859700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1831400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1801500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1794200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1819900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1318100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1418200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1433200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1267100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1237700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1190500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1259600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1274800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1227600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1265700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1241200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1237300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1311700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1271200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1251400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1238700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1306400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1334800</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5836,8 +5965,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5879,722 +6009,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E57" s="3">
         <v>48700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>61700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>46000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>63000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>69200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>76900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>73400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>56800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>80200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>78100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>63900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>63800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>61500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>57900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>58400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>51200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>45000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>49100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>50300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>43000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>49100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>48500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>50700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>52300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>57400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>60800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>63400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>62600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>57900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>65400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>55300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>41500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>41800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>39400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>43000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>48800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E58" s="3">
         <v>304700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>304300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>303900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>311700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>13600</v>
       </c>
       <c r="N58" s="3">
         <v>13600</v>
       </c>
       <c r="O58" s="3">
+        <v>13600</v>
+      </c>
+      <c r="P58" s="3">
         <v>18900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>58200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>214100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>144100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>82700</v>
-      </c>
-      <c r="V58" s="3">
-        <v>17000</v>
       </c>
       <c r="W58" s="3">
         <v>17000</v>
       </c>
       <c r="X58" s="3">
+        <v>17000</v>
+      </c>
+      <c r="Y58" s="3">
         <v>17100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>167000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>231400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>77000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>62000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>56900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>117500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>27700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>12700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>17000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>194300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>151500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>108600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>65900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>61000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>66300</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>149100</v>
+      </c>
+      <c r="E59" s="3">
         <v>134300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>134000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>145600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>140000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>139200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>150000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>137300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>128000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>132400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>124900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>112300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>104500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>153200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>142500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>115700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>169700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>160200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>160800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>162200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>186200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>134400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>122500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>128000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>147100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>142400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>125700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>115300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>144700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>131500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>118600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>111600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>135200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>131200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>104600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>100300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>107200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>101100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>282600</v>
+      </c>
+      <c r="E60" s="3">
         <v>539900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>548300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>531400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>578100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>253200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>273900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>260100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>300400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>261800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>264200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>236900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>251800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>226900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>262200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>180500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>442300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>355400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>288500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>228300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>253500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>194400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>338600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>407800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>274800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>256700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>240100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>293700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>235800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>211300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>189200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>194000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>384700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>324200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>255000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>205500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>211200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>216200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>198700</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1260500</v>
+      </c>
+      <c r="E61" s="3">
         <v>920300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>920800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>921300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>971700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1288300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1309500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1291600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>855500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>857300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>748700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>751400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>811800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>756800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>759600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>763100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>559400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>633100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>698000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>767300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>690600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>292700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>297000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>296900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>305500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>309700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>314000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>318100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>322500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>326600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>331000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>330800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>59400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>118700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>178000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>237200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>253600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>270000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>336500</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E62" s="3">
         <v>63300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>65600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>67600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>21400</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="J62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>75800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>69900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>72000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>118400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>114400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>106500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>108600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>112100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>116400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>121400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>144200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>111800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>114700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>119900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>99700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>96700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>52700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>56800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>48700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>46600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>44200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>42300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>40800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>46000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>36900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>35900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>34300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>49300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6712,8 +6861,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6831,8 +6983,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6950,127 +7105,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1599600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1579400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1593000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1579800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1630100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1624400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1646400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1635600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1235600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1257100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1117600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1097600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1116800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1102100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1136100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1050100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1110300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1100600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1102900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1117100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1088300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>598900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>750300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>824600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>680000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>663200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>606800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>668600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>606900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>584500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>564400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>567100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>484900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>488900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>469900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>478600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>499100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>535500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>585700</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7112,8 +7273,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7231,8 +7393,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7350,8 +7515,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7469,8 +7637,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7588,127 +7759,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>279300</v>
+      </c>
+      <c r="E72" s="3">
         <v>381100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>336300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>356000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>352200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>392200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>368500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>386600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>360500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>340100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>308900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>284000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>253200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>223800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>204400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>222300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>202400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>192700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>169400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>154600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>158000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>169000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>137100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>89000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>78500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>69900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>85600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>99400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>161400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>140600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>194400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>189900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>266900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>323600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>330200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>310100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>289900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>341100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>325700</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7826,8 +8003,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7945,8 +8125,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8064,127 +8247,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>796300</v>
+      </c>
+      <c r="E76" s="3">
         <v>911500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>849200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>882300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>820800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>906900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>878900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>905400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>960000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>943300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>893700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>864600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>818000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>776000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>729000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>770400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>749400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>730800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>698500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>677100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>731700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>719200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>667900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>608600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>587100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>574600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>583800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>591000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>667900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>643100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>701300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>674100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>752400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>822800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>801300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>772800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>739600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>770900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>749100</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8302,251 +8491,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>46018</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45654</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45290</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44562</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44191</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43827</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43736</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43645</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43554</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43463</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43372</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43099</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42917</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42826</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E81" s="3">
         <v>44700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>38700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>34000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>58000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>37500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>33800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>38400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>20400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>31200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>41000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>29400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>32900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>33200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>23200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>14900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>31900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>48100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>10500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>17600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>29900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>37500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>18300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>18700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-6500</v>
-      </c>
-      <c r="AK81" s="3">
-        <v>20100</v>
       </c>
       <c r="AL81" s="3">
         <v>20100</v>
       </c>
       <c r="AM81" s="3">
+        <v>20100</v>
+      </c>
+      <c r="AN81" s="3">
         <v>-51100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>15400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8588,127 +8786,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E83" s="3">
         <v>15100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>23400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>22400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>24400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>23500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>25000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>21900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>28800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>27100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>27000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>27400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>29800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>27900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>25300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>26400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>22300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>22200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>21800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>22200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>22300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8826,8 +9028,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8945,8 +9150,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9064,8 +9272,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9183,8 +9394,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9302,127 +9516,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E89" s="3">
         <v>93600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>111300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>116600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>43800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>48800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-27400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>64100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>99100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>79600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>64400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>87000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>42000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>68100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>62400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>43500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>66300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>29200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>46400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>79300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>29900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>20600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>58200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>57400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>23100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>57600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>65400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>58900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>38400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>34600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>55200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9464,127 +9684,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>2900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-36000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-45500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-35100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-26700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-48500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-19100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9702,8 +9926,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9821,127 +10048,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-86600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-33000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-139200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-268900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-25100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-36500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-31100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-58200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-34500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-20500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-429100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>37100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-23900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-45100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>6000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-13200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-27600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-26300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-14600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-17300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-19000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9983,8 +10216,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10024,8 +10258,8 @@
       <c r="O96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10102,8 +10336,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10221,8 +10458,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10340,8 +10580,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10459,361 +10702,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-101500</v>
+      </c>
+      <c r="E100" s="3">
         <v>2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-76600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-151500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-74800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>333700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-63500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>109400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-49700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-25700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-23400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>432800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-149900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-64300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>149000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>11400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-46200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-112500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>16100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>7000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-76200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>18700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-112700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>8300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-12700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-10400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-45400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3100</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>1500</v>
       </c>
       <c r="Z101" s="3">
         <v>1500</v>
       </c>
       <c r="AA101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-117900</v>
+      </c>
+      <c r="E102" s="3">
         <v>66900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-45100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>165600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-157000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>65300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>60500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-44500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>22600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>44500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>19000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-18800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-90200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>138400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>10900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-78200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>20900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>14500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>7700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>11900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>48000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>31900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>32200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>9900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>20600</v>
       </c>
     </row>
